--- a/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,15 +579,11 @@
           <t>001/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>4500011581</t>
-        </is>
+      <c r="C2" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4500011581</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -669,6 +665,310 @@
         <v>1285000</v>
       </c>
       <c r="AD2" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-20 07:34:49</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>023/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>16500000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>95</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15675000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>825000</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>16500000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>16500000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>16500000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-20 08:23:37</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>022/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>2350000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>30</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>60</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>705000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1410000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>188000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2303000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2303000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>47000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2350000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-20 08:24:55</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>90</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>8</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>32400000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2880000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>35280000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>35280000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>720000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="AD5" t="n">
         <v>98</v>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AD16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1379,15 +1379,11 @@
           <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>4500011739</t>
-        </is>
+      <c r="C10" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4500011739</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1470,6 +1466,610 @@
       </c>
       <c r="AD10" t="n">
         <v>94</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-21 09:44:21</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>033/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>15</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>28</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>48</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1875000</v>
+      </c>
+      <c r="R11" t="n">
+        <v>187500</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="V11" t="n">
+        <v>187500</v>
+      </c>
+      <c r="W11" t="n">
+        <v>250000</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>11625000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>375000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>500000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-21 10:50:13</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>205751000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>90</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>10287550</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>185175900</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>195463450</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>195463450</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>10287550</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>205751000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-21 11:23:39</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>90</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>480000</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>5880000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>5880000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>120000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-21 11:56:11</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>7920000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>98</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>7761600</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>7761600</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>7761600</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>158400</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7920000</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:42:49</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>19125000</v>
+      </c>
+      <c r="H15" t="n">
+        <v>85</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>8</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>16256250</v>
+      </c>
+      <c r="R15" t="n">
+        <v>956250</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1530000</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>17786250</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>956250</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>18742500</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>382500</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>19125000</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:19:39</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>5812675</v>
+      </c>
+      <c r="H16" t="n">
+        <v>90</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>8</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5231407.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>465014</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>5696421.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>5696421.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>116253.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>5812675</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
@@ -1171,12 +1171,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-20 10:17:26</t>
+          <t>2026-09-20 10:29:50</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1196,87 +1196,87 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>131400000</v>
+        <v>185600000</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
-        <v>6570000</v>
+        <v>27840000</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2784000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>51968000.00000001</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>111690000</v>
+        <v>89088000</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>2784000</v>
       </c>
       <c r="W8" t="n">
-        <v>10512000</v>
+        <v>3712000</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>128772000</v>
+        <v>172608000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5568000</v>
       </c>
       <c r="AA8" t="n">
-        <v>128772000</v>
+        <v>178176000</v>
       </c>
       <c r="AB8" t="n">
-        <v>2628000</v>
+        <v>7424000</v>
       </c>
       <c r="AC8" t="n">
-        <v>131400000</v>
+        <v>185600000</v>
       </c>
       <c r="AD8" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-20 10:29:50</t>
+          <t>2026-09-20 11:38:05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>185600000</v>
+        <v>193750000</v>
       </c>
       <c r="H9" t="n">
         <v>15</v>
@@ -1305,78 +1305,78 @@
         <v>1.5</v>
       </c>
       <c r="J9" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="M9" t="n">
         <v>1.5</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>27840000</v>
+        <v>29062500</v>
       </c>
       <c r="R9" t="n">
-        <v>2784000</v>
+        <v>2906250</v>
       </c>
       <c r="S9" t="n">
-        <v>51968000.00000001</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>89088000</v>
+        <v>145312500</v>
       </c>
       <c r="V9" t="n">
-        <v>2784000</v>
+        <v>2906250</v>
       </c>
       <c r="W9" t="n">
-        <v>3712000</v>
+        <v>7750000</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>172608000</v>
+        <v>182125000</v>
       </c>
       <c r="Z9" t="n">
-        <v>5568000</v>
+        <v>5812500</v>
       </c>
       <c r="AA9" t="n">
-        <v>178176000</v>
+        <v>187937500</v>
       </c>
       <c r="AB9" t="n">
-        <v>7424000</v>
+        <v>5812500</v>
       </c>
       <c r="AC9" t="n">
-        <v>185600000</v>
+        <v>193750000</v>
       </c>
       <c r="AD9" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-20 11:38:05</t>
+          <t>2026-09-21 09:44:21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>033/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1392,11 +1392,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>193750000</v>
+        <v>12500000</v>
       </c>
       <c r="H10" t="n">
         <v>15</v>
@@ -1405,78 +1405,78 @@
         <v>1.5</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="M10" t="n">
         <v>1.5</v>
       </c>
       <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>4</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3</v>
-      </c>
       <c r="Q10" t="n">
-        <v>29062500</v>
+        <v>1875000</v>
       </c>
       <c r="R10" t="n">
-        <v>2906250</v>
+        <v>187500</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3500000</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>145312500</v>
+        <v>6000000</v>
       </c>
       <c r="V10" t="n">
-        <v>2906250</v>
+        <v>187500</v>
       </c>
       <c r="W10" t="n">
-        <v>7750000</v>
+        <v>250000</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>182125000</v>
+        <v>11625000</v>
       </c>
       <c r="Z10" t="n">
-        <v>5812500</v>
+        <v>375000</v>
       </c>
       <c r="AA10" t="n">
-        <v>187937500</v>
+        <v>12000000</v>
       </c>
       <c r="AB10" t="n">
-        <v>5812500</v>
+        <v>500000</v>
       </c>
       <c r="AC10" t="n">
-        <v>193750000</v>
+        <v>12500000</v>
       </c>
       <c r="AD10" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-21 09:44:21</t>
+          <t>2026-09-21 10:50:13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>033/BSS-JOB/WS/VIII/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1492,91 +1492,91 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>12500000</v>
+        <v>205751000</v>
       </c>
       <c r="H11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1875000</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>187500</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>6000000</v>
+        <v>10287550</v>
       </c>
       <c r="V11" t="n">
-        <v>187500</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>250000</v>
+        <v>185175900</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>11625000</v>
+        <v>195463450</v>
       </c>
       <c r="Z11" t="n">
-        <v>375000</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>12000000</v>
+        <v>195463450</v>
       </c>
       <c r="AB11" t="n">
-        <v>500000</v>
+        <v>10287550</v>
       </c>
       <c r="AC11" t="n">
-        <v>12500000</v>
+        <v>205751000</v>
       </c>
       <c r="AD11" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-21 10:50:13</t>
+          <t>2026-09-21 11:23:39</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1592,14 +1592,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>205751000</v>
+        <v>6000000</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1611,22 +1611,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5400000</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1638,45 +1638,45 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>10287550</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>185175900</v>
+        <v>480000</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>195463450</v>
+        <v>5880000</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>195463450</v>
+        <v>5880000</v>
       </c>
       <c r="AB12" t="n">
-        <v>10287550</v>
+        <v>120000</v>
       </c>
       <c r="AC12" t="n">
-        <v>205751000</v>
+        <v>6000000</v>
       </c>
       <c r="AD12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-21 11:23:39</t>
+          <t>2026-09-21 11:56:11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1692,14 +1692,14 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>6000000</v>
+        <v>7920000</v>
       </c>
       <c r="H13" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
         <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>5400000</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1744,25 +1744,25 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>480000</v>
+        <v>7761600</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>5880000</v>
+        <v>7761600</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>5880000</v>
+        <v>7761600</v>
       </c>
       <c r="AB13" t="n">
-        <v>120000</v>
+        <v>158400</v>
       </c>
       <c r="AC13" t="n">
-        <v>6000000</v>
+        <v>7920000</v>
       </c>
       <c r="AD13" t="n">
         <v>98</v>
@@ -1771,19 +1771,19 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-21 11:56:11</t>
+          <t>2026-09-21 12:42:49</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>031/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>7201250141</v>
       </c>
       <c r="D14" t="n">
-        <v>4500011739</v>
+        <v>0</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1792,17 +1792,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>7920000</v>
+        <v>19125000</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1826,10 +1826,10 @@
         <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>16256250</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>956250</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -1844,39 +1844,39 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>7761600</v>
+        <v>1530000</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>7761600</v>
+        <v>17786250</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>956250</v>
       </c>
       <c r="AA14" t="n">
-        <v>7761600</v>
+        <v>18742500</v>
       </c>
       <c r="AB14" t="n">
-        <v>158400</v>
+        <v>382500</v>
       </c>
       <c r="AC14" t="n">
-        <v>7920000</v>
+        <v>19125000</v>
       </c>
       <c r="AD14" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-21 12:42:49</t>
+          <t>2026-09-21 13:19:39</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1892,17 +1892,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>19125000</v>
+        <v>5812675</v>
       </c>
       <c r="H15" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1926,10 +1926,10 @@
         <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>16256250</v>
+        <v>5231407.5</v>
       </c>
       <c r="R15" t="n">
-        <v>956250</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1944,39 +1944,39 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1530000</v>
+        <v>465014</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>17786250</v>
+        <v>5696421.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>956250</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>18742500</v>
+        <v>5696421.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>382500</v>
+        <v>116253.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>19125000</v>
+        <v>5812675</v>
       </c>
       <c r="AD15" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-21 13:19:39</t>
+          <t>2026-09-22 10:57:32</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1996,14 +1996,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>5812675</v>
+        <v>131400000</v>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2015,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2030,7 +2030,7 @@
         <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>5231407.5</v>
+        <v>6570000</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2042,31 +2042,31 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>111690000</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>465014</v>
+        <v>10512000</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>5696421.5</v>
+        <v>128772000</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>5696421.5</v>
+        <v>128772000</v>
       </c>
       <c r="AB16" t="n">
-        <v>116253.5</v>
+        <v>2628000</v>
       </c>
       <c r="AC16" t="n">
-        <v>5812675</v>
+        <v>131400000</v>
       </c>
       <c r="AD16" t="n">
         <v>98</v>

--- a/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD16"/>
+  <dimension ref="A1:AD17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1571,12 +1571,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-21 11:23:39</t>
+          <t>2026-09-21 11:56:11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1592,14 +1592,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>6000000</v>
+        <v>7920000</v>
       </c>
       <c r="H12" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1617,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1626,7 +1626,7 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>5400000</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1644,25 +1644,25 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>480000</v>
+        <v>7761600</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>5880000</v>
+        <v>7761600</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>5880000</v>
+        <v>7761600</v>
       </c>
       <c r="AB12" t="n">
-        <v>120000</v>
+        <v>158400</v>
       </c>
       <c r="AC12" t="n">
-        <v>6000000</v>
+        <v>7920000</v>
       </c>
       <c r="AD12" t="n">
         <v>98</v>
@@ -1671,19 +1671,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-21 11:56:11</t>
+          <t>2026-09-21 12:42:49</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>031/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>7201250141</v>
       </c>
       <c r="D13" t="n">
-        <v>4500011739</v>
+        <v>0</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1692,17 +1692,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>7920000</v>
+        <v>19125000</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1726,10 +1726,10 @@
         <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>16256250</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>956250</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1744,39 +1744,39 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>7761600</v>
+        <v>1530000</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>7761600</v>
+        <v>17786250</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>956250</v>
       </c>
       <c r="AA13" t="n">
-        <v>7761600</v>
+        <v>18742500</v>
       </c>
       <c r="AB13" t="n">
-        <v>158400</v>
+        <v>382500</v>
       </c>
       <c r="AC13" t="n">
-        <v>7920000</v>
+        <v>19125000</v>
       </c>
       <c r="AD13" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-21 12:42:49</t>
+          <t>2026-09-21 13:19:39</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1792,17 +1792,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>19125000</v>
+        <v>5812675</v>
       </c>
       <c r="H14" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1826,10 +1826,10 @@
         <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>16256250</v>
+        <v>5231407.5</v>
       </c>
       <c r="R14" t="n">
-        <v>956250</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -1844,46 +1844,46 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1530000</v>
+        <v>465014</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>17786250</v>
+        <v>5696421.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>956250</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>18742500</v>
+        <v>5696421.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>382500</v>
+        <v>116253.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>19125000</v>
+        <v>5812675</v>
       </c>
       <c r="AD14" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-21 13:19:39</t>
+          <t>2026-09-22 10:57:32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>7201250141</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>4500011739</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1892,14 +1892,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5812675</v>
+        <v>131400000</v>
       </c>
       <c r="H15" t="n">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1911,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1926,7 +1926,7 @@
         <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>5231407.5</v>
+        <v>6570000</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -1938,31 +1938,31 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>111690000</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>465014</v>
+        <v>10512000</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>5696421.5</v>
+        <v>128772000</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>5696421.5</v>
+        <v>128772000</v>
       </c>
       <c r="AB15" t="n">
-        <v>116253.5</v>
+        <v>2628000</v>
       </c>
       <c r="AC15" t="n">
-        <v>5812675</v>
+        <v>131400000</v>
       </c>
       <c r="AD15" t="n">
         <v>98</v>
@@ -1971,23 +1971,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-22 10:57:32</t>
+          <t>2026-09-30 12:25:43</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>4500011739</t>
-        </is>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4500011739</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1996,14 +1992,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>131400000</v>
+        <v>12000000</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2015,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2030,7 +2026,7 @@
         <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>6570000</v>
+        <v>10800000</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2042,34 +2038,138 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>111690000</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>10512000</v>
+        <v>960000</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>128772000</v>
+        <v>11760000</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>128772000</v>
+        <v>11760000</v>
       </c>
       <c r="AB16" t="n">
-        <v>2628000</v>
+        <v>240000</v>
       </c>
       <c r="AC16" t="n">
-        <v>131400000</v>
+        <v>12000000</v>
       </c>
       <c r="AD16" t="n">
         <v>98</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:24:39</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>9117360</v>
+      </c>
+      <c r="H17" t="n">
+        <v>85</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>10</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>7749756</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>911736</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8661492</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>8661492</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>455868</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9117360</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD17"/>
+  <dimension ref="A1:AD18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2079,15 +2079,11 @@
           <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C17" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -2170,6 +2166,110 @@
       </c>
       <c r="AD17" t="n">
         <v>95</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:48:13</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>035/BSS-JOB/WS/X/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>151397500</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>98</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>148369550</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>148369550</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>148369550</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>3027950</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>151397500</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD18"/>
+  <dimension ref="A1:AD20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2179,15 +2179,11 @@
           <t>035/BSS-JOB/WS/X/2026</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C18" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -2269,6 +2265,210 @@
         <v>151397500</v>
       </c>
       <c r="AD18" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-02 09:18:24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>036/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>12245000</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>98</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>12000100</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>12000100</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>12000100</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>244900</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>12245000</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-02 09:43:03</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>030/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>53762499.99999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>98</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>52687249.99999999</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>52687249.99999999</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>52687249.99999999</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1075250</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>53762499.99999999</v>
+      </c>
+      <c r="AD20" t="n">
         <v>98</v>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
@@ -2071,12 +2071,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-30 13:24:39</t>
+          <t>2026-10-01 13:48:13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>035/BSS-JOB/WS/X/2026</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2092,14 +2092,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>9117360</v>
+        <v>151397500</v>
       </c>
       <c r="H17" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2117,16 +2117,16 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>7749756</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2144,46 +2144,46 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>911736</v>
+        <v>148369550</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>8661492</v>
+        <v>148369550</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>8661492</v>
+        <v>148369550</v>
       </c>
       <c r="AB17" t="n">
-        <v>455868</v>
+        <v>3027950</v>
       </c>
       <c r="AC17" t="n">
-        <v>9117360</v>
+        <v>151397500</v>
       </c>
       <c r="AD17" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-01 13:48:13</t>
+          <t>2026-10-02 09:18:24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>035/BSS-JOB/WS/X/2026</t>
+          <t>036/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>7201250141</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>4500011739</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -2192,11 +2192,11 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>151397500</v>
+        <v>12245000</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2244,25 +2244,25 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>148369550</v>
+        <v>12000100</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>148369550</v>
+        <v>12000100</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>148369550</v>
+        <v>12000100</v>
       </c>
       <c r="AB18" t="n">
-        <v>3027950</v>
+        <v>244900</v>
       </c>
       <c r="AC18" t="n">
-        <v>151397500</v>
+        <v>12245000</v>
       </c>
       <c r="AD18" t="n">
         <v>98</v>
@@ -2271,19 +2271,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-02 09:18:24</t>
+          <t>2026-10-02 09:43:03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>036/BSS-JOB/WS/IX/2026</t>
+          <t>030/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>7201250141</v>
       </c>
-      <c r="D19" t="n">
-        <v>4500011739</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -2292,11 +2294,11 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>12245000</v>
+        <v>53762499.99999999</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2344,25 +2346,25 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>12000100</v>
+        <v>52687249.99999999</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>12000100</v>
+        <v>52687249.99999999</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>12000100</v>
+        <v>52687249.99999999</v>
       </c>
       <c r="AB19" t="n">
-        <v>244900</v>
+        <v>1075250</v>
       </c>
       <c r="AC19" t="n">
-        <v>12245000</v>
+        <v>53762499.99999999</v>
       </c>
       <c r="AD19" t="n">
         <v>98</v>
@@ -2371,12 +2373,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-02 09:43:03</t>
+          <t>2026-10-03 06:58:55</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>030/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2386,7 +2388,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2396,14 +2398,14 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>53762499.99999999</v>
+        <v>8803080</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2421,16 +2423,16 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>7482618</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2448,28 +2450,28 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>52687249.99999999</v>
+        <v>880308</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>52687249.99999999</v>
+        <v>8362926</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>52687249.99999999</v>
+        <v>8362926</v>
       </c>
       <c r="AB20" t="n">
-        <v>1075250</v>
+        <v>440154</v>
       </c>
       <c r="AC20" t="n">
-        <v>53762499.99999999</v>
+        <v>8803080</v>
       </c>
       <c r="AD20" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD20"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2381,10 +2381,8 @@
           <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="C20" t="n">
+        <v>7201250141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2471,6 +2469,110 @@
         <v>8803080</v>
       </c>
       <c r="AD20" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:01:01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>5816070</v>
+      </c>
+      <c r="H21" t="n">
+        <v>85</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4943659.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>581607</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>5525266.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>5525266.5</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>290803.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>5816070</v>
+      </c>
+      <c r="AD21" t="n">
         <v>95</v>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2483,10 +2483,8 @@
           <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="C21" t="n">
+        <v>7201250141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2574,6 +2572,212 @@
       </c>
       <c r="AD21" t="n">
         <v>95</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:58:11</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>8675000</v>
+      </c>
+      <c r="H22" t="n">
+        <v>15</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>28</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>20</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N22" t="n">
+        <v>30</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1301250</v>
+      </c>
+      <c r="R22" t="n">
+        <v>130125</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2429000</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1735000</v>
+      </c>
+      <c r="V22" t="n">
+        <v>130125</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2602500</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>8067750</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>260250</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>8328000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>347000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8675000</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:06:19</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>26475000</v>
+      </c>
+      <c r="H23" t="n">
+        <v>15</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>28</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>20</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>30</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3971250</v>
+      </c>
+      <c r="R23" t="n">
+        <v>397125</v>
+      </c>
+      <c r="S23" t="n">
+        <v>7413000.000000001</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>5295000</v>
+      </c>
+      <c r="V23" t="n">
+        <v>397125</v>
+      </c>
+      <c r="W23" t="n">
+        <v>7942500</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>24621750</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>794250</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>25416000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1059000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>26475000</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD23"/>
+  <dimension ref="A1:AD24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1771,19 +1771,19 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-21 13:19:39</t>
+          <t>2026-09-22 10:57:32</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>7201250141</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>4500011739</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1792,14 +1792,14 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>5812675</v>
+        <v>131400000</v>
       </c>
       <c r="H14" t="n">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1811,7 +1811,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
         <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>5231407.5</v>
+        <v>6570000</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1838,31 +1838,31 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>111690000</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>465014</v>
+        <v>10512000</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>5696421.5</v>
+        <v>128772000</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>5696421.5</v>
+        <v>128772000</v>
       </c>
       <c r="AB14" t="n">
-        <v>116253.5</v>
+        <v>2628000</v>
       </c>
       <c r="AC14" t="n">
-        <v>5812675</v>
+        <v>131400000</v>
       </c>
       <c r="AD14" t="n">
         <v>98</v>
@@ -1871,12 +1871,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-22 10:57:32</t>
+          <t>2026-09-30 12:25:43</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1892,14 +1892,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>131400000</v>
+        <v>12000000</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1911,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1926,7 +1926,7 @@
         <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>6570000</v>
+        <v>10800000</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -1938,31 +1938,31 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>111690000</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>10512000</v>
+        <v>960000</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>128772000</v>
+        <v>11760000</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>128772000</v>
+        <v>11760000</v>
       </c>
       <c r="AB15" t="n">
-        <v>2628000</v>
+        <v>240000</v>
       </c>
       <c r="AC15" t="n">
-        <v>131400000</v>
+        <v>12000000</v>
       </c>
       <c r="AD15" t="n">
         <v>98</v>
@@ -1971,19 +1971,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-30 12:25:43</t>
+          <t>2026-10-01 13:48:13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
+          <t>035/BSS-JOB/WS/X/2026</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>7201250141</v>
       </c>
       <c r="D16" t="n">
-        <v>4500011739</v>
+        <v>0</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1992,14 +1992,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>12000000</v>
+        <v>151397500</v>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2017,7 +2017,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2026,7 +2026,7 @@
         <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>10800000</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2044,25 +2044,25 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>960000</v>
+        <v>148369550</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>11760000</v>
+        <v>148369550</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>11760000</v>
+        <v>148369550</v>
       </c>
       <c r="AB16" t="n">
-        <v>240000</v>
+        <v>3027950</v>
       </c>
       <c r="AC16" t="n">
-        <v>12000000</v>
+        <v>151397500</v>
       </c>
       <c r="AD16" t="n">
         <v>98</v>
@@ -2071,19 +2071,19 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-01 13:48:13</t>
+          <t>2026-10-02 09:18:24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>035/BSS-JOB/WS/X/2026</t>
+          <t>036/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>7201250141</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>4500011739</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -2092,11 +2092,11 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>151397500</v>
+        <v>12245000</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -2144,25 +2144,25 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>148369550</v>
+        <v>12000100</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>148369550</v>
+        <v>12000100</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>148369550</v>
+        <v>12000100</v>
       </c>
       <c r="AB17" t="n">
-        <v>3027950</v>
+        <v>244900</v>
       </c>
       <c r="AC17" t="n">
-        <v>151397500</v>
+        <v>12245000</v>
       </c>
       <c r="AD17" t="n">
         <v>98</v>
@@ -2171,19 +2171,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-02 09:18:24</t>
+          <t>2026-10-02 09:43:03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>036/BSS-JOB/WS/IX/2026</t>
+          <t>030/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>7201250141</v>
       </c>
-      <c r="D18" t="n">
-        <v>4500011739</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -2192,11 +2194,11 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>12245000</v>
+        <v>53762499.99999999</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2244,25 +2246,25 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>12000100</v>
+        <v>52687249.99999999</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>12000100</v>
+        <v>52687249.99999999</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>12000100</v>
+        <v>52687249.99999999</v>
       </c>
       <c r="AB18" t="n">
-        <v>244900</v>
+        <v>1075250</v>
       </c>
       <c r="AC18" t="n">
-        <v>12245000</v>
+        <v>53762499.99999999</v>
       </c>
       <c r="AD18" t="n">
         <v>98</v>
@@ -2271,12 +2273,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-02 09:43:03</t>
+          <t>2026-10-03 06:58:55</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>030/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2284,7 +2286,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2294,14 +2296,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>53762499.99999999</v>
+        <v>8803080</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2319,16 +2321,16 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>7482618</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2346,39 +2348,39 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>52687249.99999999</v>
+        <v>880308</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>52687249.99999999</v>
+        <v>8362926</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>52687249.99999999</v>
+        <v>8362926</v>
       </c>
       <c r="AB19" t="n">
-        <v>1075250</v>
+        <v>440154</v>
       </c>
       <c r="AC19" t="n">
-        <v>53762499.99999999</v>
+        <v>8803080</v>
       </c>
       <c r="AD19" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-03 06:58:55</t>
+          <t>2026-10-03 12:01:01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2396,11 +2398,11 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>8803080</v>
+        <v>5816070</v>
       </c>
       <c r="H20" t="n">
         <v>85</v>
@@ -2430,7 +2432,7 @@
         <v>5</v>
       </c>
       <c r="Q20" t="n">
-        <v>7482618</v>
+        <v>4943659.5</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2448,25 +2450,25 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>880308</v>
+        <v>581607</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>8362926</v>
+        <v>5525266.5</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>8362926</v>
+        <v>5525266.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>440154</v>
+        <v>290803.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>8803080</v>
+        <v>5816070</v>
       </c>
       <c r="AD20" t="n">
         <v>95</v>
@@ -2475,12 +2477,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-03 12:01:01</t>
+          <t>2026-10-03 12:58:11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2488,7 +2490,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2498,91 +2500,91 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>5816070</v>
+        <v>8675000</v>
       </c>
       <c r="H21" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N21" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q21" t="n">
-        <v>4943659.5</v>
+        <v>1301250</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>130125</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2429000</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1735000</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>130125</v>
       </c>
       <c r="W21" t="n">
-        <v>581607</v>
+        <v>2602500</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>5525266.5</v>
+        <v>8067750</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>260250</v>
       </c>
       <c r="AA21" t="n">
-        <v>5525266.5</v>
+        <v>8328000</v>
       </c>
       <c r="AB21" t="n">
-        <v>290803.5</v>
+        <v>347000</v>
       </c>
       <c r="AC21" t="n">
-        <v>5816070</v>
+        <v>8675000</v>
       </c>
       <c r="AD21" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-03 12:58:11</t>
+          <t>2026-10-03 13:06:19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2600,11 +2602,11 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>8675000</v>
+        <v>26475000</v>
       </c>
       <c r="H22" t="n">
         <v>15</v>
@@ -2634,43 +2636,43 @@
         <v>4</v>
       </c>
       <c r="Q22" t="n">
-        <v>1301250</v>
+        <v>3971250</v>
       </c>
       <c r="R22" t="n">
-        <v>130125</v>
+        <v>397125</v>
       </c>
       <c r="S22" t="n">
-        <v>2429000</v>
+        <v>7413000.000000001</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1735000</v>
+        <v>5295000</v>
       </c>
       <c r="V22" t="n">
-        <v>130125</v>
+        <v>397125</v>
       </c>
       <c r="W22" t="n">
-        <v>2602500</v>
+        <v>7942500</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>8067750</v>
+        <v>24621750</v>
       </c>
       <c r="Z22" t="n">
-        <v>260250</v>
+        <v>794250</v>
       </c>
       <c r="AA22" t="n">
-        <v>8328000</v>
+        <v>25416000</v>
       </c>
       <c r="AB22" t="n">
-        <v>347000</v>
+        <v>1059000</v>
       </c>
       <c r="AC22" t="n">
-        <v>8675000</v>
+        <v>26475000</v>
       </c>
       <c r="AD22" t="n">
         <v>93</v>
@@ -2679,105 +2681,207 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-03 13:06:19</t>
+          <t>2026-10-05 09:24:55</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>5816070</v>
+      </c>
+      <c r="H23" t="n">
+        <v>90</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5234463</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>465285.6</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>5699748.6</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>5699748.6</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>116321.4</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>5816070</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:53:51</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>7201250141</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>26475000</v>
-      </c>
-      <c r="H23" t="n">
-        <v>15</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>28</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>20</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N23" t="n">
-        <v>30</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3971250</v>
-      </c>
-      <c r="R23" t="n">
-        <v>397125</v>
-      </c>
-      <c r="S23" t="n">
-        <v>7413000.000000001</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>5295000</v>
-      </c>
-      <c r="V23" t="n">
-        <v>397125</v>
-      </c>
-      <c r="W23" t="n">
-        <v>7942500</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>24621750</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>794250</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>25416000</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1059000</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>26475000</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>93</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>5816070</v>
+      </c>
+      <c r="H24" t="n">
+        <v>90</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>8</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>5234463</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>465285.6</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>5699748.6</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>5699748.6</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>116321.4</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>5816070</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD24"/>
+  <dimension ref="A1:AD32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2791,10 +2791,8 @@
           <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="C24" t="n">
+        <v>7201250141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2882,6 +2880,824 @@
       </c>
       <c r="AD24" t="n">
         <v>98</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:53:55</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>256729500</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>95</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>243893025</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>243893025</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>243893025</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>12836475</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>256729500</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-06 10:09:56</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>040/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>22500000</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>95</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>5</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>21375000</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1125000</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>22500000</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>22500000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>22500000</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-06 10:40:42</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>041/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>95</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>42750000</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2250000</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:22:10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>120000000</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>95</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>114000000</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>120000000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>120000000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>120000000</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:43:08</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>043/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>95</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>5</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>14250000</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>750000</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:31:17</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>044/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>95</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>5</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>11400000</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>600000</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:00:47</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>045/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>337500000</v>
+      </c>
+      <c r="H31" t="n">
+        <v>15</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>75</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>50625000</v>
+      </c>
+      <c r="R31" t="n">
+        <v>5062500</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>253125000</v>
+      </c>
+      <c r="V31" t="n">
+        <v>5062500</v>
+      </c>
+      <c r="W31" t="n">
+        <v>13500000</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>317250000</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>10125000</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>327375000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>10125000</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>337500000</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:29:23</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>198400000</v>
+      </c>
+      <c r="H32" t="n">
+        <v>15</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>28</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>48</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>29760000</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2976000</v>
+      </c>
+      <c r="S32" t="n">
+        <v>55552000.00000001</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>95232000</v>
+      </c>
+      <c r="V32" t="n">
+        <v>2976000</v>
+      </c>
+      <c r="W32" t="n">
+        <v>3968000</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>184512000</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>5952000</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>190464000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>7936000</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>198400000</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD32"/>
+  <dimension ref="A1:AD36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3607,10 +3607,8 @@
           <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="C32" t="n">
+        <v>7201250141</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3698,6 +3696,416 @@
       </c>
       <c r="AD32" t="n">
         <v>93</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:26:05</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>192500000</v>
+      </c>
+      <c r="H33" t="n">
+        <v>5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>85</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>8</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>9625000</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>163625000</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>15400000</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>188650000</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>188650000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>3850000</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>192500000</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:58:13</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>048/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>11460000</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>98</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>11230800</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>11230800</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>11230800</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>229200</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>11460000</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-06 18:53:41</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>049/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>15488550</v>
+      </c>
+      <c r="H35" t="n">
+        <v>90</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>8</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>13939695</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1239084</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>15178779</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>15178779</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>309771</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>15488550</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-06 19:07:28</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>050/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>69000000</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>98</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>67620000</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>67620000</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>67620000</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1380000</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>69000000</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
@@ -3701,12 +3701,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-06 17:26:05</t>
+          <t>2026-10-06 17:58:13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>192500000</v>
+        <v>11460000</v>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3743,13 +3743,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -3758,7 +3758,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>9625000</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -3770,31 +3770,31 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>163625000</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>15400000</v>
+        <v>11230800</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>188650000</v>
+        <v>11230800</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>188650000</v>
+        <v>11230800</v>
       </c>
       <c r="AB33" t="n">
-        <v>3850000</v>
+        <v>229200</v>
       </c>
       <c r="AC33" t="n">
-        <v>192500000</v>
+        <v>11460000</v>
       </c>
       <c r="AD33" t="n">
         <v>98</v>
@@ -3803,12 +3803,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-06 17:58:13</t>
+          <t>2026-10-06 18:53:41</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>11460000</v>
+        <v>15488550</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -3851,7 +3851,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>13939695</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -3878,25 +3878,25 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>11230800</v>
+        <v>1239084</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>11230800</v>
+        <v>15178779</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>11230800</v>
+        <v>15178779</v>
       </c>
       <c r="AB34" t="n">
-        <v>229200</v>
+        <v>309771</v>
       </c>
       <c r="AC34" t="n">
-        <v>11460000</v>
+        <v>15488550</v>
       </c>
       <c r="AD34" t="n">
         <v>98</v>
@@ -3905,12 +3905,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-06 18:53:41</t>
+          <t>2026-10-06 19:07:28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>050/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3928,14 +3928,14 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>15488550</v>
+        <v>69000000</v>
       </c>
       <c r="H35" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3953,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -3962,7 +3962,7 @@
         <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>13939695</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3980,25 +3980,25 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1239084</v>
+        <v>67620000</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>15178779</v>
+        <v>67620000</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>15178779</v>
+        <v>67620000</v>
       </c>
       <c r="AB35" t="n">
-        <v>309771</v>
+        <v>1380000</v>
       </c>
       <c r="AC35" t="n">
-        <v>15488550</v>
+        <v>69000000</v>
       </c>
       <c r="AD35" t="n">
         <v>98</v>
@@ -4007,12 +4007,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-06 19:07:28</t>
+          <t>2026-10-07 06:17:59</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>050/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4032,14 +4032,14 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>69000000</v>
+        <v>192500000</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -4051,13 +4051,13 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4066,7 +4066,7 @@
         <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>9625000</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4078,31 +4078,31 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>163625000</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>67620000</v>
+        <v>15400000</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>67620000</v>
+        <v>188650000</v>
       </c>
       <c r="Z36" t="n">
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>67620000</v>
+        <v>188650000</v>
       </c>
       <c r="AB36" t="n">
-        <v>1380000</v>
+        <v>3850000</v>
       </c>
       <c r="AC36" t="n">
-        <v>69000000</v>
+        <v>192500000</v>
       </c>
       <c r="AD36" t="n">
         <v>98</v>

--- a/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD36"/>
+  <dimension ref="A1:AD40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4015,10 +4015,8 @@
           <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="C36" t="n">
+        <v>7201250141</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4106,6 +4104,416 @@
       </c>
       <c r="AD36" t="n">
         <v>98</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-07 08:44:05</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="H37" t="n">
+        <v>15</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>28</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>48</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2250000</v>
+      </c>
+      <c r="R37" t="n">
+        <v>225000</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="V37" t="n">
+        <v>225000</v>
+      </c>
+      <c r="W37" t="n">
+        <v>300000</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>13950000</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>450000</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>14400000</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>600000</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:02:12</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>15200000</v>
+      </c>
+      <c r="H38" t="n">
+        <v>15</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J38" t="n">
+        <v>28</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>48</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2280000</v>
+      </c>
+      <c r="R38" t="n">
+        <v>228000</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4256000</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>7296000</v>
+      </c>
+      <c r="V38" t="n">
+        <v>228000</v>
+      </c>
+      <c r="W38" t="n">
+        <v>304000</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>14136000</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>456000</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>14592000</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>608000</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>15200000</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:34:34</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>30245000</v>
+      </c>
+      <c r="H39" t="n">
+        <v>15</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J39" t="n">
+        <v>28</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>48</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>4536750</v>
+      </c>
+      <c r="R39" t="n">
+        <v>453675</v>
+      </c>
+      <c r="S39" t="n">
+        <v>8468600</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>14517600</v>
+      </c>
+      <c r="V39" t="n">
+        <v>453675</v>
+      </c>
+      <c r="W39" t="n">
+        <v>604900</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>28127850</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>907350</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>29035200</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1209800</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>30245000</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:43:34</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>32335000</v>
+      </c>
+      <c r="H40" t="n">
+        <v>15</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J40" t="n">
+        <v>28</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>48</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>4850250</v>
+      </c>
+      <c r="R40" t="n">
+        <v>485025</v>
+      </c>
+      <c r="S40" t="n">
+        <v>9053800</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>15520800</v>
+      </c>
+      <c r="V40" t="n">
+        <v>485025</v>
+      </c>
+      <c r="W40" t="n">
+        <v>646700</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>30071550</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>970050</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>31041600</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1293400</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>32335000</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD40"/>
+  <dimension ref="A1:AD41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2885,12 +2885,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-06 09:53:55</t>
+          <t>2026-10-06 10:09:56</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>040/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>256729500</v>
+        <v>22500000</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2933,13 +2933,13 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>21375000</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2960,39 +2960,39 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>243893025</v>
+        <v>1125000</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>243893025</v>
+        <v>22500000</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>243893025</v>
+        <v>22500000</v>
       </c>
       <c r="AB25" t="n">
-        <v>12836475</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>256729500</v>
+        <v>22500000</v>
       </c>
       <c r="AD25" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-06 10:09:56</t>
+          <t>2026-10-06 10:40:42</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>040/BSS-JOB/WS/IX/2026</t>
+          <t>041/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>22500000</v>
+        <v>45000000</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -3050,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>21375000</v>
+        <v>42750000</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -3062,25 +3062,25 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1125000</v>
+        <v>2250000</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>22500000</v>
+        <v>45000000</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>22500000</v>
+        <v>45000000</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>22500000</v>
+        <v>45000000</v>
       </c>
       <c r="AD26" t="n">
         <v>100</v>
@@ -3089,12 +3089,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-06 10:40:42</t>
+          <t>2026-10-06 11:22:10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>041/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>45000000</v>
+        <v>120000000</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -3152,7 +3152,7 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>42750000</v>
+        <v>114000000</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
@@ -3164,25 +3164,25 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>2250000</v>
+        <v>6000000</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>45000000</v>
+        <v>120000000</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>45000000</v>
+        <v>120000000</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>45000000</v>
+        <v>120000000</v>
       </c>
       <c r="AD27" t="n">
         <v>100</v>
@@ -3191,12 +3191,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-06 11:22:10</t>
+          <t>2026-10-06 11:43:08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>043/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3214,11 +3214,11 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>120000000</v>
+        <v>15000000</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>114000000</v>
+        <v>14250000</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -3266,25 +3266,25 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>6000000</v>
+        <v>750000</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>120000000</v>
+        <v>15000000</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>120000000</v>
+        <v>15000000</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>120000000</v>
+        <v>15000000</v>
       </c>
       <c r="AD28" t="n">
         <v>100</v>
@@ -3293,12 +3293,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-06 11:43:08</t>
+          <t>2026-10-06 12:31:17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/WS/IX/2026</t>
+          <t>044/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3316,11 +3316,11 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>15000000</v>
+        <v>12000000</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>14250000</v>
+        <v>11400000</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -3368,25 +3368,25 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>750000</v>
+        <v>600000</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>15000000</v>
+        <v>12000000</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>15000000</v>
+        <v>12000000</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>15000000</v>
+        <v>12000000</v>
       </c>
       <c r="AD29" t="n">
         <v>100</v>
@@ -3395,12 +3395,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-06 12:31:17</t>
+          <t>2026-10-06 13:00:47</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>044/BSS-JOB/WS/IX/2026</t>
+          <t>045/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -3418,91 +3418,91 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>12000000</v>
+        <v>337500000</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>50625000</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>5062500</v>
       </c>
       <c r="S30" t="n">
-        <v>11400000</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>253125000</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>5062500</v>
       </c>
       <c r="W30" t="n">
-        <v>600000</v>
+        <v>13500000</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>12000000</v>
+        <v>317250000</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>10125000</v>
       </c>
       <c r="AA30" t="n">
-        <v>12000000</v>
+        <v>327375000</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>10125000</v>
       </c>
       <c r="AC30" t="n">
-        <v>12000000</v>
+        <v>337500000</v>
       </c>
       <c r="AD30" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-06 13:00:47</t>
+          <t>2026-10-06 13:29:23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>045/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>337500000</v>
+        <v>198400000</v>
       </c>
       <c r="H31" t="n">
         <v>15</v>
@@ -3533,78 +3533,78 @@
         <v>1.5</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="M31" t="n">
         <v>1.5</v>
       </c>
       <c r="N31" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
         <v>4</v>
       </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>3</v>
-      </c>
       <c r="Q31" t="n">
-        <v>50625000</v>
+        <v>29760000</v>
       </c>
       <c r="R31" t="n">
-        <v>5062500</v>
+        <v>2976000</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>55552000.00000001</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>253125000</v>
+        <v>95232000</v>
       </c>
       <c r="V31" t="n">
-        <v>5062500</v>
+        <v>2976000</v>
       </c>
       <c r="W31" t="n">
-        <v>13500000</v>
+        <v>3968000</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>317250000</v>
+        <v>184512000</v>
       </c>
       <c r="Z31" t="n">
-        <v>10125000</v>
+        <v>5952000</v>
       </c>
       <c r="AA31" t="n">
-        <v>327375000</v>
+        <v>190464000</v>
       </c>
       <c r="AB31" t="n">
-        <v>10125000</v>
+        <v>7936000</v>
       </c>
       <c r="AC31" t="n">
-        <v>337500000</v>
+        <v>198400000</v>
       </c>
       <c r="AD31" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-06 13:29:23</t>
+          <t>2026-10-06 17:58:13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -3626,87 +3626,87 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>198400000</v>
+        <v>11460000</v>
       </c>
       <c r="H32" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
+        <v>98</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
         <v>2</v>
       </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>4</v>
-      </c>
       <c r="Q32" t="n">
-        <v>29760000</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2976000</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>55552000.00000001</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>95232000</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>2976000</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>3968000</v>
+        <v>11230800</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>184512000</v>
+        <v>11230800</v>
       </c>
       <c r="Z32" t="n">
-        <v>5952000</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>190464000</v>
+        <v>11230800</v>
       </c>
       <c r="AB32" t="n">
-        <v>7936000</v>
+        <v>229200</v>
       </c>
       <c r="AC32" t="n">
-        <v>198400000</v>
+        <v>11460000</v>
       </c>
       <c r="AD32" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-06 17:58:13</t>
+          <t>2026-10-06 18:53:41</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>11460000</v>
+        <v>15488550</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -3758,7 +3758,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>13939695</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -3776,25 +3776,25 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>11230800</v>
+        <v>1239084</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>11230800</v>
+        <v>15178779</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>11230800</v>
+        <v>15178779</v>
       </c>
       <c r="AB33" t="n">
-        <v>229200</v>
+        <v>309771</v>
       </c>
       <c r="AC33" t="n">
-        <v>11460000</v>
+        <v>15488550</v>
       </c>
       <c r="AD33" t="n">
         <v>98</v>
@@ -3803,12 +3803,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-06 18:53:41</t>
+          <t>2026-10-06 19:07:28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>050/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3826,14 +3826,14 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>15488550</v>
+        <v>69000000</v>
       </c>
       <c r="H34" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -3851,7 +3851,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>13939695</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -3878,25 +3878,25 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1239084</v>
+        <v>67620000</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>15178779</v>
+        <v>67620000</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>15178779</v>
+        <v>67620000</v>
       </c>
       <c r="AB34" t="n">
-        <v>309771</v>
+        <v>1380000</v>
       </c>
       <c r="AC34" t="n">
-        <v>15488550</v>
+        <v>69000000</v>
       </c>
       <c r="AD34" t="n">
         <v>98</v>
@@ -3905,12 +3905,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-06 19:07:28</t>
+          <t>2026-10-07 06:17:59</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>050/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3928,14 +3928,14 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>69000000</v>
+        <v>192500000</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3947,13 +3947,13 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -3962,7 +3962,7 @@
         <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>9625000</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3974,31 +3974,31 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>163625000</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>67620000</v>
+        <v>15400000</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>67620000</v>
+        <v>188650000</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>67620000</v>
+        <v>188650000</v>
       </c>
       <c r="AB35" t="n">
-        <v>1380000</v>
+        <v>3850000</v>
       </c>
       <c r="AC35" t="n">
-        <v>69000000</v>
+        <v>192500000</v>
       </c>
       <c r="AD35" t="n">
         <v>98</v>
@@ -4007,12 +4007,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-07 06:17:59</t>
+          <t>2026-10-07 08:44:05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4030,91 +4030,91 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>192500000</v>
+        <v>15000000</v>
       </c>
       <c r="H36" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N36" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q36" t="n">
-        <v>9625000</v>
+        <v>2250000</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>225000</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>4200000</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>163625000</v>
+        <v>7200000</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>225000</v>
       </c>
       <c r="W36" t="n">
-        <v>15400000</v>
+        <v>300000</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>188650000</v>
+        <v>13950000</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>450000</v>
       </c>
       <c r="AA36" t="n">
-        <v>188650000</v>
+        <v>14400000</v>
       </c>
       <c r="AB36" t="n">
-        <v>3850000</v>
+        <v>600000</v>
       </c>
       <c r="AC36" t="n">
-        <v>192500000</v>
+        <v>15000000</v>
       </c>
       <c r="AD36" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-07 08:44:05</t>
+          <t>2026-10-07 09:02:12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>15000000</v>
+        <v>15200000</v>
       </c>
       <c r="H37" t="n">
         <v>15</v>
@@ -4166,43 +4166,43 @@
         <v>4</v>
       </c>
       <c r="Q37" t="n">
-        <v>2250000</v>
+        <v>2280000</v>
       </c>
       <c r="R37" t="n">
-        <v>225000</v>
+        <v>228000</v>
       </c>
       <c r="S37" t="n">
-        <v>4200000</v>
+        <v>4256000</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>7200000</v>
+        <v>7296000</v>
       </c>
       <c r="V37" t="n">
-        <v>225000</v>
+        <v>228000</v>
       </c>
       <c r="W37" t="n">
-        <v>300000</v>
+        <v>304000</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>13950000</v>
+        <v>14136000</v>
       </c>
       <c r="Z37" t="n">
-        <v>450000</v>
+        <v>456000</v>
       </c>
       <c r="AA37" t="n">
-        <v>14400000</v>
+        <v>14592000</v>
       </c>
       <c r="AB37" t="n">
-        <v>600000</v>
+        <v>608000</v>
       </c>
       <c r="AC37" t="n">
-        <v>15000000</v>
+        <v>15200000</v>
       </c>
       <c r="AD37" t="n">
         <v>93</v>
@@ -4211,12 +4211,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-07 09:02:12</t>
+          <t>2026-10-07 09:34:34</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4234,11 +4234,11 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>15200000</v>
+        <v>30245000</v>
       </c>
       <c r="H38" t="n">
         <v>15</v>
@@ -4268,43 +4268,43 @@
         <v>4</v>
       </c>
       <c r="Q38" t="n">
-        <v>2280000</v>
+        <v>4536750</v>
       </c>
       <c r="R38" t="n">
-        <v>228000</v>
+        <v>453675</v>
       </c>
       <c r="S38" t="n">
-        <v>4256000</v>
+        <v>8468600</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>7296000</v>
+        <v>14517600</v>
       </c>
       <c r="V38" t="n">
-        <v>228000</v>
+        <v>453675</v>
       </c>
       <c r="W38" t="n">
-        <v>304000</v>
+        <v>604900</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>14136000</v>
+        <v>28127850</v>
       </c>
       <c r="Z38" t="n">
-        <v>456000</v>
+        <v>907350</v>
       </c>
       <c r="AA38" t="n">
-        <v>14592000</v>
+        <v>29035200</v>
       </c>
       <c r="AB38" t="n">
-        <v>608000</v>
+        <v>1209800</v>
       </c>
       <c r="AC38" t="n">
-        <v>15200000</v>
+        <v>30245000</v>
       </c>
       <c r="AD38" t="n">
         <v>93</v>
@@ -4313,12 +4313,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-07 09:34:34</t>
+          <t>2026-10-07 10:43:34</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -4336,11 +4336,11 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>30245000</v>
+        <v>32335000</v>
       </c>
       <c r="H39" t="n">
         <v>15</v>
@@ -4370,43 +4370,43 @@
         <v>4</v>
       </c>
       <c r="Q39" t="n">
-        <v>4536750</v>
+        <v>4850250</v>
       </c>
       <c r="R39" t="n">
-        <v>453675</v>
+        <v>485025</v>
       </c>
       <c r="S39" t="n">
-        <v>8468600</v>
+        <v>9053800</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>14517600</v>
+        <v>15520800</v>
       </c>
       <c r="V39" t="n">
-        <v>453675</v>
+        <v>485025</v>
       </c>
       <c r="W39" t="n">
-        <v>604900</v>
+        <v>646700</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>28127850</v>
+        <v>30071550</v>
       </c>
       <c r="Z39" t="n">
-        <v>907350</v>
+        <v>970050</v>
       </c>
       <c r="AA39" t="n">
-        <v>29035200</v>
+        <v>31041600</v>
       </c>
       <c r="AB39" t="n">
-        <v>1209800</v>
+        <v>1293400</v>
       </c>
       <c r="AC39" t="n">
-        <v>30245000</v>
+        <v>32335000</v>
       </c>
       <c r="AD39" t="n">
         <v>93</v>
@@ -4415,18 +4415,16 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-07 10:43:34</t>
+          <t>2026-10-07 11:30:14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>7201250141</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4440,11 +4438,11 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>32335000</v>
+        <v>20720000</v>
       </c>
       <c r="H40" t="n">
         <v>15</v>
@@ -4474,46 +4472,150 @@
         <v>4</v>
       </c>
       <c r="Q40" t="n">
-        <v>4850250</v>
+        <v>3108000</v>
       </c>
       <c r="R40" t="n">
-        <v>485025</v>
+        <v>310800</v>
       </c>
       <c r="S40" t="n">
-        <v>9053800</v>
+        <v>5801600.000000001</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>15520800</v>
+        <v>9945600</v>
       </c>
       <c r="V40" t="n">
-        <v>485025</v>
+        <v>310800</v>
       </c>
       <c r="W40" t="n">
-        <v>646700</v>
+        <v>414400</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>30071550</v>
+        <v>19269600</v>
       </c>
       <c r="Z40" t="n">
-        <v>970050</v>
+        <v>621600</v>
       </c>
       <c r="AA40" t="n">
-        <v>31041600</v>
+        <v>19891200</v>
       </c>
       <c r="AB40" t="n">
-        <v>1293400</v>
+        <v>828800</v>
       </c>
       <c r="AC40" t="n">
-        <v>32335000</v>
+        <v>20720000</v>
       </c>
       <c r="AD40" t="n">
         <v>93</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-07 11:58:54</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>256779000</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>95</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>243940050</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>243940050</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>243940050</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>12838950</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>256779000</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
@@ -3497,12 +3497,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-06 13:29:23</t>
+          <t>2026-10-06 17:58:13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -3524,87 +3524,87 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>198400000</v>
+        <v>11460000</v>
       </c>
       <c r="H31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
+        <v>98</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
         <v>2</v>
       </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>4</v>
-      </c>
       <c r="Q31" t="n">
-        <v>29760000</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2976000</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>55552000.00000001</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>95232000</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>2976000</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>3968000</v>
+        <v>11230800</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>184512000</v>
+        <v>11230800</v>
       </c>
       <c r="Z31" t="n">
-        <v>5952000</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>190464000</v>
+        <v>11230800</v>
       </c>
       <c r="AB31" t="n">
-        <v>7936000</v>
+        <v>229200</v>
       </c>
       <c r="AC31" t="n">
-        <v>198400000</v>
+        <v>11460000</v>
       </c>
       <c r="AD31" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-06 17:58:13</t>
+          <t>2026-10-06 18:53:41</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>11460000</v>
+        <v>15488550</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3647,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -3656,7 +3656,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>13939695</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3674,25 +3674,25 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>11230800</v>
+        <v>1239084</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>11230800</v>
+        <v>15178779</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>11230800</v>
+        <v>15178779</v>
       </c>
       <c r="AB32" t="n">
-        <v>229200</v>
+        <v>309771</v>
       </c>
       <c r="AC32" t="n">
-        <v>11460000</v>
+        <v>15488550</v>
       </c>
       <c r="AD32" t="n">
         <v>98</v>
@@ -3701,12 +3701,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-06 18:53:41</t>
+          <t>2026-10-06 19:07:28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>050/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3724,14 +3724,14 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>15488550</v>
+        <v>69000000</v>
       </c>
       <c r="H33" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -3758,7 +3758,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>13939695</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -3776,25 +3776,25 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1239084</v>
+        <v>67620000</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>15178779</v>
+        <v>67620000</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>15178779</v>
+        <v>67620000</v>
       </c>
       <c r="AB33" t="n">
-        <v>309771</v>
+        <v>1380000</v>
       </c>
       <c r="AC33" t="n">
-        <v>15488550</v>
+        <v>69000000</v>
       </c>
       <c r="AD33" t="n">
         <v>98</v>
@@ -3803,12 +3803,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-06 19:07:28</t>
+          <t>2026-10-07 06:17:59</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>050/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3826,14 +3826,14 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>69000000</v>
+        <v>192500000</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -3845,13 +3845,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>9625000</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -3872,31 +3872,31 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>163625000</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>67620000</v>
+        <v>15400000</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>67620000</v>
+        <v>188650000</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>67620000</v>
+        <v>188650000</v>
       </c>
       <c r="AB34" t="n">
-        <v>1380000</v>
+        <v>3850000</v>
       </c>
       <c r="AC34" t="n">
-        <v>69000000</v>
+        <v>192500000</v>
       </c>
       <c r="AD34" t="n">
         <v>98</v>
@@ -3905,12 +3905,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-07 06:17:59</t>
+          <t>2026-10-07 08:44:05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3928,91 +3928,91 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>192500000</v>
+        <v>15000000</v>
       </c>
       <c r="H35" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N35" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q35" t="n">
-        <v>9625000</v>
+        <v>2250000</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>225000</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>4200000</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>163625000</v>
+        <v>7200000</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>225000</v>
       </c>
       <c r="W35" t="n">
-        <v>15400000</v>
+        <v>300000</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>188650000</v>
+        <v>13950000</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>450000</v>
       </c>
       <c r="AA35" t="n">
-        <v>188650000</v>
+        <v>14400000</v>
       </c>
       <c r="AB35" t="n">
-        <v>3850000</v>
+        <v>600000</v>
       </c>
       <c r="AC35" t="n">
-        <v>192500000</v>
+        <v>15000000</v>
       </c>
       <c r="AD35" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-07 08:44:05</t>
+          <t>2026-10-07 09:02:12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>15000000</v>
+        <v>15200000</v>
       </c>
       <c r="H36" t="n">
         <v>15</v>
@@ -4064,43 +4064,43 @@
         <v>4</v>
       </c>
       <c r="Q36" t="n">
-        <v>2250000</v>
+        <v>2280000</v>
       </c>
       <c r="R36" t="n">
-        <v>225000</v>
+        <v>228000</v>
       </c>
       <c r="S36" t="n">
-        <v>4200000</v>
+        <v>4256000</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>7200000</v>
+        <v>7296000</v>
       </c>
       <c r="V36" t="n">
-        <v>225000</v>
+        <v>228000</v>
       </c>
       <c r="W36" t="n">
-        <v>300000</v>
+        <v>304000</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>13950000</v>
+        <v>14136000</v>
       </c>
       <c r="Z36" t="n">
-        <v>450000</v>
+        <v>456000</v>
       </c>
       <c r="AA36" t="n">
-        <v>14400000</v>
+        <v>14592000</v>
       </c>
       <c r="AB36" t="n">
-        <v>600000</v>
+        <v>608000</v>
       </c>
       <c r="AC36" t="n">
-        <v>15000000</v>
+        <v>15200000</v>
       </c>
       <c r="AD36" t="n">
         <v>93</v>
@@ -4109,12 +4109,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-07 09:02:12</t>
+          <t>2026-10-07 09:34:34</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4132,11 +4132,11 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>15200000</v>
+        <v>30245000</v>
       </c>
       <c r="H37" t="n">
         <v>15</v>
@@ -4166,43 +4166,43 @@
         <v>4</v>
       </c>
       <c r="Q37" t="n">
-        <v>2280000</v>
+        <v>4536750</v>
       </c>
       <c r="R37" t="n">
-        <v>228000</v>
+        <v>453675</v>
       </c>
       <c r="S37" t="n">
-        <v>4256000</v>
+        <v>8468600</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>7296000</v>
+        <v>14517600</v>
       </c>
       <c r="V37" t="n">
-        <v>228000</v>
+        <v>453675</v>
       </c>
       <c r="W37" t="n">
-        <v>304000</v>
+        <v>604900</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>14136000</v>
+        <v>28127850</v>
       </c>
       <c r="Z37" t="n">
-        <v>456000</v>
+        <v>907350</v>
       </c>
       <c r="AA37" t="n">
-        <v>14592000</v>
+        <v>29035200</v>
       </c>
       <c r="AB37" t="n">
-        <v>608000</v>
+        <v>1209800</v>
       </c>
       <c r="AC37" t="n">
-        <v>15200000</v>
+        <v>30245000</v>
       </c>
       <c r="AD37" t="n">
         <v>93</v>
@@ -4211,12 +4211,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-07 09:34:34</t>
+          <t>2026-10-07 10:43:34</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4234,11 +4234,11 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>30245000</v>
+        <v>32335000</v>
       </c>
       <c r="H38" t="n">
         <v>15</v>
@@ -4268,43 +4268,43 @@
         <v>4</v>
       </c>
       <c r="Q38" t="n">
-        <v>4536750</v>
+        <v>4850250</v>
       </c>
       <c r="R38" t="n">
-        <v>453675</v>
+        <v>485025</v>
       </c>
       <c r="S38" t="n">
-        <v>8468600</v>
+        <v>9053800</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>14517600</v>
+        <v>15520800</v>
       </c>
       <c r="V38" t="n">
-        <v>453675</v>
+        <v>485025</v>
       </c>
       <c r="W38" t="n">
-        <v>604900</v>
+        <v>646700</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>28127850</v>
+        <v>30071550</v>
       </c>
       <c r="Z38" t="n">
-        <v>907350</v>
+        <v>970050</v>
       </c>
       <c r="AA38" t="n">
-        <v>29035200</v>
+        <v>31041600</v>
       </c>
       <c r="AB38" t="n">
-        <v>1209800</v>
+        <v>1293400</v>
       </c>
       <c r="AC38" t="n">
-        <v>30245000</v>
+        <v>32335000</v>
       </c>
       <c r="AD38" t="n">
         <v>93</v>
@@ -4313,12 +4313,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-07 10:43:34</t>
+          <t>2026-10-07 11:30:14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -4336,11 +4336,11 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>32335000</v>
+        <v>20720000</v>
       </c>
       <c r="H39" t="n">
         <v>15</v>
@@ -4370,43 +4370,43 @@
         <v>4</v>
       </c>
       <c r="Q39" t="n">
-        <v>4850250</v>
+        <v>3108000</v>
       </c>
       <c r="R39" t="n">
-        <v>485025</v>
+        <v>310800</v>
       </c>
       <c r="S39" t="n">
-        <v>9053800</v>
+        <v>5801600.000000001</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>15520800</v>
+        <v>9945600</v>
       </c>
       <c r="V39" t="n">
-        <v>485025</v>
+        <v>310800</v>
       </c>
       <c r="W39" t="n">
-        <v>646700</v>
+        <v>414400</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>30071550</v>
+        <v>19269600</v>
       </c>
       <c r="Z39" t="n">
-        <v>970050</v>
+        <v>621600</v>
       </c>
       <c r="AA39" t="n">
-        <v>31041600</v>
+        <v>19891200</v>
       </c>
       <c r="AB39" t="n">
-        <v>1293400</v>
+        <v>828800</v>
       </c>
       <c r="AC39" t="n">
-        <v>32335000</v>
+        <v>20720000</v>
       </c>
       <c r="AD39" t="n">
         <v>93</v>
@@ -4415,12 +4415,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-07 11:30:14</t>
+          <t>2026-10-07 11:58:54</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4438,91 +4438,91 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>20720000</v>
+        <v>256779000</v>
       </c>
       <c r="H40" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q40" t="n">
-        <v>3108000</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>310800</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>5801600.000000001</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>9945600</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>310800</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>414400</v>
+        <v>243940050</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>19269600</v>
+        <v>243940050</v>
       </c>
       <c r="Z40" t="n">
-        <v>621600</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>19891200</v>
+        <v>243940050</v>
       </c>
       <c r="AB40" t="n">
-        <v>828800</v>
+        <v>12838950</v>
       </c>
       <c r="AC40" t="n">
-        <v>20720000</v>
+        <v>256779000</v>
       </c>
       <c r="AD40" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-07 11:58:54</t>
+          <t>2026-10-10 08:59:37</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4546,76 +4546,76 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>256779000</v>
+        <v>198400000</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N41" t="n">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>29760000</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2976000</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>55552000.00000001</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>95232000</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>2976000</v>
       </c>
       <c r="W41" t="n">
-        <v>243940050</v>
+        <v>3968000</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>243940050</v>
+        <v>184512000</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>5952000</v>
       </c>
       <c r="AA41" t="n">
-        <v>243940050</v>
+        <v>190464000</v>
       </c>
       <c r="AB41" t="n">
-        <v>12838950</v>
+        <v>7936000</v>
       </c>
       <c r="AC41" t="n">
-        <v>256779000</v>
+        <v>198400000</v>
       </c>
       <c r="AD41" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD41"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4525,10 +4525,8 @@
           <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="C41" t="n">
+        <v>7201250141</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4616,6 +4614,212 @@
       </c>
       <c r="AD41" t="n">
         <v>93</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:28:24</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>051/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1725000</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>98</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1690500</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1690500</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1690500</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>34500</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1725000</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:36:37</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>052/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>8625000</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>98</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>8452500</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>8452500</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>8452500</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>172500</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>8625000</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AD45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4729,10 +4729,8 @@
           <t>052/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="C43" t="n">
+        <v>7201250141</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4820,6 +4818,212 @@
       </c>
       <c r="AD43" t="n">
         <v>98</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:26:40</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>002/BSS-JOB/WS/I/2026</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>4500011794</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1437500</v>
+      </c>
+      <c r="H44" t="n">
+        <v>90</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>8</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1293750</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>115000</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1408750</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1408750</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>28750</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1437500</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:54:24</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>021/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>4500011795</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>517499.9999999999</v>
+      </c>
+      <c r="H45" t="n">
+        <v>85</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>10</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>439874.9999999999</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>51749.99999999999</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>491624.9999999999</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>491624.9999999999</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>25875</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>517499.9999999999</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
@@ -1471,12 +1471,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-21 10:50:13</t>
+          <t>2026-09-21 11:56:11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>205751000</v>
+        <v>7920000</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1511,19 +1511,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1538,52 +1538,52 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>10287550</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>185175900</v>
+        <v>7761600</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>195463450</v>
+        <v>7761600</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>195463450</v>
+        <v>7761600</v>
       </c>
       <c r="AB11" t="n">
-        <v>10287550</v>
+        <v>158400</v>
       </c>
       <c r="AC11" t="n">
-        <v>205751000</v>
+        <v>7920000</v>
       </c>
       <c r="AD11" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-21 11:56:11</t>
+          <t>2026-09-21 12:42:49</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>031/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>7201250141</v>
       </c>
       <c r="D12" t="n">
-        <v>4500011739</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1592,17 +1592,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>7920000</v>
+        <v>19125000</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1617,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1626,10 +1626,10 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>16256250</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>956250</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1644,46 +1644,46 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>7761600</v>
+        <v>1530000</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>7761600</v>
+        <v>17786250</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>956250</v>
       </c>
       <c r="AA12" t="n">
-        <v>7761600</v>
+        <v>18742500</v>
       </c>
       <c r="AB12" t="n">
-        <v>158400</v>
+        <v>382500</v>
       </c>
       <c r="AC12" t="n">
-        <v>7920000</v>
+        <v>19125000</v>
       </c>
       <c r="AD12" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-21 12:42:49</t>
+          <t>2026-09-22 10:57:32</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>7201250141</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>4500011739</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1692,26 +1692,26 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>19125000</v>
+        <v>131400000</v>
       </c>
       <c r="H13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>85</v>
-      </c>
-      <c r="I13" t="n">
-        <v>5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1726,10 +1726,10 @@
         <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>16256250</v>
+        <v>6570000</v>
       </c>
       <c r="R13" t="n">
-        <v>956250</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1738,45 +1738,45 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>111690000</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1530000</v>
+        <v>10512000</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>17786250</v>
+        <v>128772000</v>
       </c>
       <c r="Z13" t="n">
-        <v>956250</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>18742500</v>
+        <v>128772000</v>
       </c>
       <c r="AB13" t="n">
-        <v>382500</v>
+        <v>2628000</v>
       </c>
       <c r="AC13" t="n">
-        <v>19125000</v>
+        <v>131400000</v>
       </c>
       <c r="AD13" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-22 10:57:32</t>
+          <t>2026-09-30 12:25:43</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1792,14 +1792,14 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>131400000</v>
+        <v>12000000</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1811,7 +1811,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
         <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>6570000</v>
+        <v>10800000</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1838,31 +1838,31 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>111690000</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>10512000</v>
+        <v>960000</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>128772000</v>
+        <v>11760000</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>128772000</v>
+        <v>11760000</v>
       </c>
       <c r="AB14" t="n">
-        <v>2628000</v>
+        <v>240000</v>
       </c>
       <c r="AC14" t="n">
-        <v>131400000</v>
+        <v>12000000</v>
       </c>
       <c r="AD14" t="n">
         <v>98</v>
@@ -1871,19 +1871,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-30 12:25:43</t>
+          <t>2026-10-01 13:48:13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
+          <t>035/BSS-JOB/WS/X/2026</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>7201250141</v>
       </c>
       <c r="D15" t="n">
-        <v>4500011739</v>
+        <v>0</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1892,14 +1892,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>12000000</v>
+        <v>151397500</v>
       </c>
       <c r="H15" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -1926,7 +1926,7 @@
         <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>10800000</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -1944,25 +1944,25 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>960000</v>
+        <v>148369550</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>11760000</v>
+        <v>148369550</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>11760000</v>
+        <v>148369550</v>
       </c>
       <c r="AB15" t="n">
-        <v>240000</v>
+        <v>3027950</v>
       </c>
       <c r="AC15" t="n">
-        <v>12000000</v>
+        <v>151397500</v>
       </c>
       <c r="AD15" t="n">
         <v>98</v>
@@ -1971,19 +1971,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-01 13:48:13</t>
+          <t>2026-10-02 09:18:24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>035/BSS-JOB/WS/X/2026</t>
+          <t>036/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>7201250141</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>4500011739</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1992,11 +1992,11 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>151397500</v>
+        <v>12245000</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -2044,25 +2044,25 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>148369550</v>
+        <v>12000100</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>148369550</v>
+        <v>12000100</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>148369550</v>
+        <v>12000100</v>
       </c>
       <c r="AB16" t="n">
-        <v>3027950</v>
+        <v>244900</v>
       </c>
       <c r="AC16" t="n">
-        <v>151397500</v>
+        <v>12245000</v>
       </c>
       <c r="AD16" t="n">
         <v>98</v>
@@ -2071,19 +2071,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-02 09:18:24</t>
+          <t>2026-10-02 09:43:03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>036/BSS-JOB/WS/IX/2026</t>
+          <t>030/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>7201250141</v>
       </c>
-      <c r="D17" t="n">
-        <v>4500011739</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -2092,11 +2094,11 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>12245000</v>
+        <v>53762499.99999999</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -2144,25 +2146,25 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>12000100</v>
+        <v>52687249.99999999</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>12000100</v>
+        <v>52687249.99999999</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>12000100</v>
+        <v>52687249.99999999</v>
       </c>
       <c r="AB17" t="n">
-        <v>244900</v>
+        <v>1075250</v>
       </c>
       <c r="AC17" t="n">
-        <v>12245000</v>
+        <v>53762499.99999999</v>
       </c>
       <c r="AD17" t="n">
         <v>98</v>
@@ -2171,12 +2173,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-02 09:43:03</t>
+          <t>2026-10-03 06:58:55</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>030/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2184,7 +2186,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2194,14 +2196,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>53762499.99999999</v>
+        <v>8803080</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2219,16 +2221,16 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>7482618</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2246,39 +2248,39 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>52687249.99999999</v>
+        <v>880308</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>52687249.99999999</v>
+        <v>8362926</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>52687249.99999999</v>
+        <v>8362926</v>
       </c>
       <c r="AB18" t="n">
-        <v>1075250</v>
+        <v>440154</v>
       </c>
       <c r="AC18" t="n">
-        <v>53762499.99999999</v>
+        <v>8803080</v>
       </c>
       <c r="AD18" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-03 06:58:55</t>
+          <t>2026-10-03 12:01:01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2296,11 +2298,11 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>8803080</v>
+        <v>5816070</v>
       </c>
       <c r="H19" t="n">
         <v>85</v>
@@ -2330,7 +2332,7 @@
         <v>5</v>
       </c>
       <c r="Q19" t="n">
-        <v>7482618</v>
+        <v>4943659.5</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2348,25 +2350,25 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>880308</v>
+        <v>581607</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>8362926</v>
+        <v>5525266.5</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>8362926</v>
+        <v>5525266.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>440154</v>
+        <v>290803.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>8803080</v>
+        <v>5816070</v>
       </c>
       <c r="AD19" t="n">
         <v>95</v>
@@ -2375,12 +2377,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-03 12:01:01</t>
+          <t>2026-10-03 12:58:11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2388,7 +2390,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2398,91 +2400,91 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>5816070</v>
+        <v>8675000</v>
       </c>
       <c r="H20" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N20" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q20" t="n">
-        <v>4943659.5</v>
+        <v>1301250</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>130125</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2429000</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1735000</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>130125</v>
       </c>
       <c r="W20" t="n">
-        <v>581607</v>
+        <v>2602500</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>5525266.5</v>
+        <v>8067750</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>260250</v>
       </c>
       <c r="AA20" t="n">
-        <v>5525266.5</v>
+        <v>8328000</v>
       </c>
       <c r="AB20" t="n">
-        <v>290803.5</v>
+        <v>347000</v>
       </c>
       <c r="AC20" t="n">
-        <v>5816070</v>
+        <v>8675000</v>
       </c>
       <c r="AD20" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-03 12:58:11</t>
+          <t>2026-10-03 13:06:19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2500,11 +2502,11 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>8675000</v>
+        <v>26475000</v>
       </c>
       <c r="H21" t="n">
         <v>15</v>
@@ -2534,43 +2536,43 @@
         <v>4</v>
       </c>
       <c r="Q21" t="n">
-        <v>1301250</v>
+        <v>3971250</v>
       </c>
       <c r="R21" t="n">
-        <v>130125</v>
+        <v>397125</v>
       </c>
       <c r="S21" t="n">
-        <v>2429000</v>
+        <v>7413000.000000001</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1735000</v>
+        <v>5295000</v>
       </c>
       <c r="V21" t="n">
-        <v>130125</v>
+        <v>397125</v>
       </c>
       <c r="W21" t="n">
-        <v>2602500</v>
+        <v>7942500</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>8067750</v>
+        <v>24621750</v>
       </c>
       <c r="Z21" t="n">
-        <v>260250</v>
+        <v>794250</v>
       </c>
       <c r="AA21" t="n">
-        <v>8328000</v>
+        <v>25416000</v>
       </c>
       <c r="AB21" t="n">
-        <v>347000</v>
+        <v>1059000</v>
       </c>
       <c r="AC21" t="n">
-        <v>8675000</v>
+        <v>26475000</v>
       </c>
       <c r="AD21" t="n">
         <v>93</v>
@@ -2579,12 +2581,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-03 13:06:19</t>
+          <t>2026-10-05 09:24:55</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2592,7 +2594,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2602,91 +2604,91 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>26475000</v>
+        <v>5816070</v>
       </c>
       <c r="H22" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3971250</v>
+        <v>5234463</v>
       </c>
       <c r="R22" t="n">
-        <v>397125</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>7413000.000000001</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>5295000</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>397125</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>7942500</v>
+        <v>465285.6</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>24621750</v>
+        <v>5699748.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>794250</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>25416000</v>
+        <v>5699748.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>1059000</v>
+        <v>116321.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>26475000</v>
+        <v>5816070</v>
       </c>
       <c r="AD22" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-05 09:24:55</t>
+          <t>2026-10-05 09:53:51</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2704,7 +2706,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2783,12 +2785,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-05 09:53:51</t>
+          <t>2026-10-06 10:09:56</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>040/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2796,7 +2798,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2806,20 +2808,20 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>5816070</v>
+        <v>22500000</v>
       </c>
       <c r="H24" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2831,22 +2833,22 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>5234463</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>21375000</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -2858,39 +2860,39 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>465285.6</v>
+        <v>1125000</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>5699748.6</v>
+        <v>22500000</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>5699748.6</v>
+        <v>22500000</v>
       </c>
       <c r="AB24" t="n">
-        <v>116321.4</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>5816070</v>
+        <v>22500000</v>
       </c>
       <c r="AD24" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-06 10:09:56</t>
+          <t>2026-10-06 10:40:42</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>040/BSS-JOB/WS/IX/2026</t>
+          <t>041/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2912,7 +2914,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>22500000</v>
+        <v>45000000</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -2948,7 +2950,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>21375000</v>
+        <v>42750000</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2960,25 +2962,25 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1125000</v>
+        <v>2250000</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>22500000</v>
+        <v>45000000</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>22500000</v>
+        <v>45000000</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>22500000</v>
+        <v>45000000</v>
       </c>
       <c r="AD25" t="n">
         <v>100</v>
@@ -2987,12 +2989,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-06 10:40:42</t>
+          <t>2026-10-06 11:22:10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>041/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3014,7 +3016,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>45000000</v>
+        <v>120000000</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -3050,7 +3052,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>42750000</v>
+        <v>114000000</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -3062,25 +3064,25 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>2250000</v>
+        <v>6000000</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>45000000</v>
+        <v>120000000</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>45000000</v>
+        <v>120000000</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>45000000</v>
+        <v>120000000</v>
       </c>
       <c r="AD26" t="n">
         <v>100</v>
@@ -3089,12 +3091,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-06 11:22:10</t>
+          <t>2026-10-06 11:43:08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>043/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3112,11 +3114,11 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>120000000</v>
+        <v>15000000</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -3152,7 +3154,7 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>114000000</v>
+        <v>14250000</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
@@ -3164,25 +3166,25 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>6000000</v>
+        <v>750000</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>120000000</v>
+        <v>15000000</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>120000000</v>
+        <v>15000000</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>120000000</v>
+        <v>15000000</v>
       </c>
       <c r="AD27" t="n">
         <v>100</v>
@@ -3191,12 +3193,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-06 11:43:08</t>
+          <t>2026-10-06 12:31:17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/WS/IX/2026</t>
+          <t>044/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3214,11 +3216,11 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>15000000</v>
+        <v>12000000</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -3254,7 +3256,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>14250000</v>
+        <v>11400000</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -3266,25 +3268,25 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>750000</v>
+        <v>600000</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>15000000</v>
+        <v>12000000</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>15000000</v>
+        <v>12000000</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>15000000</v>
+        <v>12000000</v>
       </c>
       <c r="AD28" t="n">
         <v>100</v>
@@ -3293,12 +3295,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-06 12:31:17</t>
+          <t>2026-10-06 13:00:47</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>044/BSS-JOB/WS/IX/2026</t>
+          <t>045/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3316,91 +3318,91 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>12000000</v>
+        <v>337500000</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>50625000</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>5062500</v>
       </c>
       <c r="S29" t="n">
-        <v>11400000</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>253125000</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>5062500</v>
       </c>
       <c r="W29" t="n">
-        <v>600000</v>
+        <v>13500000</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>12000000</v>
+        <v>317250000</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>10125000</v>
       </c>
       <c r="AA29" t="n">
-        <v>12000000</v>
+        <v>327375000</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>10125000</v>
       </c>
       <c r="AC29" t="n">
-        <v>12000000</v>
+        <v>337500000</v>
       </c>
       <c r="AD29" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-06 13:00:47</t>
+          <t>2026-10-06 17:58:13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>045/BSS-JOB/WS/IX/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -3422,13 +3424,13 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>337500000</v>
+        <v>11460000</v>
       </c>
       <c r="H30" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3437,25 +3439,25 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>50625000</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>5062500</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -3464,45 +3466,45 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>253125000</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>5062500</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>13500000</v>
+        <v>11230800</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>317250000</v>
+        <v>11230800</v>
       </c>
       <c r="Z30" t="n">
-        <v>10125000</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>327375000</v>
+        <v>11230800</v>
       </c>
       <c r="AB30" t="n">
-        <v>10125000</v>
+        <v>229200</v>
       </c>
       <c r="AC30" t="n">
-        <v>337500000</v>
+        <v>11460000</v>
       </c>
       <c r="AD30" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-06 17:58:13</t>
+          <t>2026-10-06 18:53:41</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -3510,7 +3512,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3524,10 +3526,10 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>11460000</v>
+        <v>15488550</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -3545,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -3554,7 +3556,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>13939695</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3572,25 +3574,25 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>11230800</v>
+        <v>1239084</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>11230800</v>
+        <v>15178779</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>11230800</v>
+        <v>15178779</v>
       </c>
       <c r="AB31" t="n">
-        <v>229200</v>
+        <v>309771</v>
       </c>
       <c r="AC31" t="n">
-        <v>11460000</v>
+        <v>15488550</v>
       </c>
       <c r="AD31" t="n">
         <v>98</v>
@@ -3599,12 +3601,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-06 18:53:41</t>
+          <t>2026-10-06 19:07:28</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>050/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -3622,14 +3624,14 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>15488550</v>
+        <v>69000000</v>
       </c>
       <c r="H32" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3647,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -3656,7 +3658,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>13939695</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3674,25 +3676,25 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1239084</v>
+        <v>67620000</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>15178779</v>
+        <v>67620000</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>15178779</v>
+        <v>67620000</v>
       </c>
       <c r="AB32" t="n">
-        <v>309771</v>
+        <v>1380000</v>
       </c>
       <c r="AC32" t="n">
-        <v>15488550</v>
+        <v>69000000</v>
       </c>
       <c r="AD32" t="n">
         <v>98</v>
@@ -3701,12 +3703,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-06 19:07:28</t>
+          <t>2026-10-07 06:17:59</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>050/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3714,7 +3716,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3724,14 +3726,14 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>69000000</v>
+        <v>192500000</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3743,13 +3745,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -3758,7 +3760,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>9625000</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -3770,31 +3772,31 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>163625000</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>67620000</v>
+        <v>15400000</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>67620000</v>
+        <v>188650000</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>67620000</v>
+        <v>188650000</v>
       </c>
       <c r="AB33" t="n">
-        <v>1380000</v>
+        <v>3850000</v>
       </c>
       <c r="AC33" t="n">
-        <v>69000000</v>
+        <v>192500000</v>
       </c>
       <c r="AD33" t="n">
         <v>98</v>
@@ -3803,12 +3805,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-07 06:17:59</t>
+          <t>2026-10-07 08:44:05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3826,91 +3828,91 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>192500000</v>
+        <v>15000000</v>
       </c>
       <c r="H34" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q34" t="n">
-        <v>9625000</v>
+        <v>2250000</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>225000</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>4200000</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>163625000</v>
+        <v>7200000</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>225000</v>
       </c>
       <c r="W34" t="n">
-        <v>15400000</v>
+        <v>300000</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>188650000</v>
+        <v>13950000</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>450000</v>
       </c>
       <c r="AA34" t="n">
-        <v>188650000</v>
+        <v>14400000</v>
       </c>
       <c r="AB34" t="n">
-        <v>3850000</v>
+        <v>600000</v>
       </c>
       <c r="AC34" t="n">
-        <v>192500000</v>
+        <v>15000000</v>
       </c>
       <c r="AD34" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-07 08:44:05</t>
+          <t>2026-10-07 09:02:12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3918,7 +3920,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3932,7 +3934,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>15000000</v>
+        <v>15200000</v>
       </c>
       <c r="H35" t="n">
         <v>15</v>
@@ -3962,43 +3964,43 @@
         <v>4</v>
       </c>
       <c r="Q35" t="n">
-        <v>2250000</v>
+        <v>2280000</v>
       </c>
       <c r="R35" t="n">
-        <v>225000</v>
+        <v>228000</v>
       </c>
       <c r="S35" t="n">
-        <v>4200000</v>
+        <v>4256000</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>7200000</v>
+        <v>7296000</v>
       </c>
       <c r="V35" t="n">
-        <v>225000</v>
+        <v>228000</v>
       </c>
       <c r="W35" t="n">
-        <v>300000</v>
+        <v>304000</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>13950000</v>
+        <v>14136000</v>
       </c>
       <c r="Z35" t="n">
-        <v>450000</v>
+        <v>456000</v>
       </c>
       <c r="AA35" t="n">
-        <v>14400000</v>
+        <v>14592000</v>
       </c>
       <c r="AB35" t="n">
-        <v>600000</v>
+        <v>608000</v>
       </c>
       <c r="AC35" t="n">
-        <v>15000000</v>
+        <v>15200000</v>
       </c>
       <c r="AD35" t="n">
         <v>93</v>
@@ -4007,12 +4009,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-07 09:02:12</t>
+          <t>2026-10-07 09:34:34</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4030,11 +4032,11 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>15200000</v>
+        <v>30245000</v>
       </c>
       <c r="H36" t="n">
         <v>15</v>
@@ -4064,43 +4066,43 @@
         <v>4</v>
       </c>
       <c r="Q36" t="n">
-        <v>2280000</v>
+        <v>4536750</v>
       </c>
       <c r="R36" t="n">
-        <v>228000</v>
+        <v>453675</v>
       </c>
       <c r="S36" t="n">
-        <v>4256000</v>
+        <v>8468600</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>7296000</v>
+        <v>14517600</v>
       </c>
       <c r="V36" t="n">
-        <v>228000</v>
+        <v>453675</v>
       </c>
       <c r="W36" t="n">
-        <v>304000</v>
+        <v>604900</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>14136000</v>
+        <v>28127850</v>
       </c>
       <c r="Z36" t="n">
-        <v>456000</v>
+        <v>907350</v>
       </c>
       <c r="AA36" t="n">
-        <v>14592000</v>
+        <v>29035200</v>
       </c>
       <c r="AB36" t="n">
-        <v>608000</v>
+        <v>1209800</v>
       </c>
       <c r="AC36" t="n">
-        <v>15200000</v>
+        <v>30245000</v>
       </c>
       <c r="AD36" t="n">
         <v>93</v>
@@ -4109,12 +4111,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-07 09:34:34</t>
+          <t>2026-10-07 10:43:34</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4132,11 +4134,11 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>30245000</v>
+        <v>32335000</v>
       </c>
       <c r="H37" t="n">
         <v>15</v>
@@ -4166,43 +4168,43 @@
         <v>4</v>
       </c>
       <c r="Q37" t="n">
-        <v>4536750</v>
+        <v>4850250</v>
       </c>
       <c r="R37" t="n">
-        <v>453675</v>
+        <v>485025</v>
       </c>
       <c r="S37" t="n">
-        <v>8468600</v>
+        <v>9053800</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>14517600</v>
+        <v>15520800</v>
       </c>
       <c r="V37" t="n">
-        <v>453675</v>
+        <v>485025</v>
       </c>
       <c r="W37" t="n">
-        <v>604900</v>
+        <v>646700</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>28127850</v>
+        <v>30071550</v>
       </c>
       <c r="Z37" t="n">
-        <v>907350</v>
+        <v>970050</v>
       </c>
       <c r="AA37" t="n">
-        <v>29035200</v>
+        <v>31041600</v>
       </c>
       <c r="AB37" t="n">
-        <v>1209800</v>
+        <v>1293400</v>
       </c>
       <c r="AC37" t="n">
-        <v>30245000</v>
+        <v>32335000</v>
       </c>
       <c r="AD37" t="n">
         <v>93</v>
@@ -4211,12 +4213,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-07 10:43:34</t>
+          <t>2026-10-07 11:30:14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4234,11 +4236,11 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>32335000</v>
+        <v>20720000</v>
       </c>
       <c r="H38" t="n">
         <v>15</v>
@@ -4268,43 +4270,43 @@
         <v>4</v>
       </c>
       <c r="Q38" t="n">
-        <v>4850250</v>
+        <v>3108000</v>
       </c>
       <c r="R38" t="n">
-        <v>485025</v>
+        <v>310800</v>
       </c>
       <c r="S38" t="n">
-        <v>9053800</v>
+        <v>5801600.000000001</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>15520800</v>
+        <v>9945600</v>
       </c>
       <c r="V38" t="n">
-        <v>485025</v>
+        <v>310800</v>
       </c>
       <c r="W38" t="n">
-        <v>646700</v>
+        <v>414400</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>30071550</v>
+        <v>19269600</v>
       </c>
       <c r="Z38" t="n">
-        <v>970050</v>
+        <v>621600</v>
       </c>
       <c r="AA38" t="n">
-        <v>31041600</v>
+        <v>19891200</v>
       </c>
       <c r="AB38" t="n">
-        <v>1293400</v>
+        <v>828800</v>
       </c>
       <c r="AC38" t="n">
-        <v>32335000</v>
+        <v>20720000</v>
       </c>
       <c r="AD38" t="n">
         <v>93</v>
@@ -4313,12 +4315,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-07 11:30:14</t>
+          <t>2026-10-10 08:59:37</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -4326,7 +4328,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4336,11 +4338,11 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>20720000</v>
+        <v>198400000</v>
       </c>
       <c r="H39" t="n">
         <v>15</v>
@@ -4370,43 +4372,43 @@
         <v>4</v>
       </c>
       <c r="Q39" t="n">
-        <v>3108000</v>
+        <v>29760000</v>
       </c>
       <c r="R39" t="n">
-        <v>310800</v>
+        <v>2976000</v>
       </c>
       <c r="S39" t="n">
-        <v>5801600.000000001</v>
+        <v>55552000.00000001</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>9945600</v>
+        <v>95232000</v>
       </c>
       <c r="V39" t="n">
-        <v>310800</v>
+        <v>2976000</v>
       </c>
       <c r="W39" t="n">
-        <v>414400</v>
+        <v>3968000</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>19269600</v>
+        <v>184512000</v>
       </c>
       <c r="Z39" t="n">
-        <v>621600</v>
+        <v>5952000</v>
       </c>
       <c r="AA39" t="n">
-        <v>19891200</v>
+        <v>190464000</v>
       </c>
       <c r="AB39" t="n">
-        <v>828800</v>
+        <v>7936000</v>
       </c>
       <c r="AC39" t="n">
-        <v>20720000</v>
+        <v>198400000</v>
       </c>
       <c r="AD39" t="n">
         <v>93</v>
@@ -4415,12 +4417,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-07 11:58:54</t>
+          <t>2026-10-13 10:28:24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>051/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -4428,7 +4430,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4438,11 +4440,11 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>256779000</v>
+        <v>1725000</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -4463,13 +4465,13 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -4490,39 +4492,39 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>243940050</v>
+        <v>1690500</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>243940050</v>
+        <v>1690500</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>243940050</v>
+        <v>1690500</v>
       </c>
       <c r="AB40" t="n">
-        <v>12838950</v>
+        <v>34500</v>
       </c>
       <c r="AC40" t="n">
-        <v>256779000</v>
+        <v>1725000</v>
       </c>
       <c r="AD40" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-10 08:59:37</t>
+          <t>2026-10-13 10:36:37</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>052/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -4530,7 +4532,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4540,91 +4542,91 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>198400000</v>
+        <v>8625000</v>
       </c>
       <c r="H41" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
+        <v>98</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
         <v>2</v>
       </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>4</v>
-      </c>
       <c r="Q41" t="n">
-        <v>29760000</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2976000</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>55552000.00000001</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>95232000</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>2976000</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>3968000</v>
+        <v>8452500</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>184512000</v>
+        <v>8452500</v>
       </c>
       <c r="Z41" t="n">
-        <v>5952000</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>190464000</v>
+        <v>8452500</v>
       </c>
       <c r="AB41" t="n">
-        <v>7936000</v>
+        <v>172500</v>
       </c>
       <c r="AC41" t="n">
-        <v>198400000</v>
+        <v>8625000</v>
       </c>
       <c r="AD41" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-13 10:28:24</t>
+          <t>2026-10-14 13:26:40</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>051/BSS-JOB/WS/VIII/2026</t>
+          <t>002/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -4632,7 +4634,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011794</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4642,14 +4644,14 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1725000</v>
+        <v>1437500</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -4667,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -4676,7 +4678,7 @@
         <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1293750</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -4694,25 +4696,25 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1690500</v>
+        <v>115000</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1690500</v>
+        <v>1408750</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1690500</v>
+        <v>1408750</v>
       </c>
       <c r="AB42" t="n">
-        <v>34500</v>
+        <v>28750</v>
       </c>
       <c r="AC42" t="n">
-        <v>1725000</v>
+        <v>1437500</v>
       </c>
       <c r="AD42" t="n">
         <v>98</v>
@@ -4721,12 +4723,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-13 10:36:37</t>
+          <t>2026-10-14 13:54:24</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>052/BSS-JOB/WS/IX/2026</t>
+          <t>021/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -4734,7 +4736,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011795</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4744,14 +4746,14 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>8625000</v>
+        <v>517499.9999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -4769,16 +4771,16 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>439874.9999999999</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -4796,39 +4798,39 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>8452500</v>
+        <v>51749.99999999999</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>8452500</v>
+        <v>491624.9999999999</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>8452500</v>
+        <v>491624.9999999999</v>
       </c>
       <c r="AB43" t="n">
-        <v>172500</v>
+        <v>25875</v>
       </c>
       <c r="AC43" t="n">
-        <v>8625000</v>
+        <v>517499.9999999999</v>
       </c>
       <c r="AD43" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-14 13:26:40</t>
+          <t>2026-10-15 17:39:32</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/WS/I/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -4836,51 +4838,51 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4500011794</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1437500</v>
+        <v>205751000</v>
       </c>
       <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>5</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
         <v>90</v>
       </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>8</v>
-      </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q44" t="n">
-        <v>1293750</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -4892,45 +4894,45 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>10287550</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>115000</v>
+        <v>185175900</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1408750</v>
+        <v>195463450</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1408750</v>
+        <v>195463450</v>
       </c>
       <c r="AB44" t="n">
-        <v>28750</v>
+        <v>10287550</v>
       </c>
       <c r="AC44" t="n">
-        <v>1437500</v>
+        <v>205751000</v>
       </c>
       <c r="AD44" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-14 13:54:24</t>
+          <t>2026-10-15 17:45:36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>021/BSS-JOB/WS/IX/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4940,24 +4942,24 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4500011795</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>517499.9999999999</v>
+        <v>256779000</v>
       </c>
       <c r="H45" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4975,7 +4977,7 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -4984,7 +4986,7 @@
         <v>5</v>
       </c>
       <c r="Q45" t="n">
-        <v>439874.9999999999</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5002,25 +5004,25 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>51749.99999999999</v>
+        <v>243940050</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>491624.9999999999</v>
+        <v>243940050</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>491624.9999999999</v>
+        <v>243940050</v>
       </c>
       <c r="AB45" t="n">
-        <v>25875</v>
+        <v>12838950</v>
       </c>
       <c r="AC45" t="n">
-        <v>517499.9999999999</v>
+        <v>256779000</v>
       </c>
       <c r="AD45" t="n">
         <v>95</v>

--- a/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_tkdn_tersimpan.xlsx
@@ -2173,12 +2173,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-03 06:58:55</t>
+          <t>2026-10-03 12:58:11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2196,91 +2196,91 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>8803080</v>
+        <v>8675000</v>
       </c>
       <c r="H18" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N18" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="n">
-        <v>7482618</v>
+        <v>1301250</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>130125</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2429000</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1735000</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>130125</v>
       </c>
       <c r="W18" t="n">
-        <v>880308</v>
+        <v>2602500</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>8362926</v>
+        <v>8067750</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>260250</v>
       </c>
       <c r="AA18" t="n">
-        <v>8362926</v>
+        <v>8328000</v>
       </c>
       <c r="AB18" t="n">
-        <v>440154</v>
+        <v>347000</v>
       </c>
       <c r="AC18" t="n">
-        <v>8803080</v>
+        <v>8675000</v>
       </c>
       <c r="AD18" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-03 12:01:01</t>
+          <t>2026-10-03 13:06:19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2298,91 +2298,91 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>5816070</v>
+        <v>26475000</v>
       </c>
       <c r="H19" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N19" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="n">
-        <v>4943659.5</v>
+        <v>3971250</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>397125</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>7413000.000000001</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>5295000</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>397125</v>
       </c>
       <c r="W19" t="n">
-        <v>581607</v>
+        <v>7942500</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>5525266.5</v>
+        <v>24621750</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>794250</v>
       </c>
       <c r="AA19" t="n">
-        <v>5525266.5</v>
+        <v>25416000</v>
       </c>
       <c r="AB19" t="n">
-        <v>290803.5</v>
+        <v>1059000</v>
       </c>
       <c r="AC19" t="n">
-        <v>5816070</v>
+        <v>26475000</v>
       </c>
       <c r="AD19" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-03 12:58:11</t>
+          <t>2026-10-06 10:09:56</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>040/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2400,91 +2400,91 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>8675000</v>
+        <v>22500000</v>
       </c>
       <c r="H20" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1301250</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>130125</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2429000</v>
+        <v>21375000</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1735000</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>130125</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2602500</v>
+        <v>1125000</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>8067750</v>
+        <v>22500000</v>
       </c>
       <c r="Z20" t="n">
-        <v>260250</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>8328000</v>
+        <v>22500000</v>
       </c>
       <c r="AB20" t="n">
-        <v>347000</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>8675000</v>
+        <v>22500000</v>
       </c>
       <c r="AD20" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-03 13:06:19</t>
+          <t>2026-10-06 10:40:42</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>041/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2502,91 +2502,91 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>26475000</v>
+        <v>45000000</v>
       </c>
       <c r="H21" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3971250</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>397125</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>7413000.000000001</v>
+        <v>42750000</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>5295000</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>397125</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>7942500</v>
+        <v>2250000</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>24621750</v>
+        <v>45000000</v>
       </c>
       <c r="Z21" t="n">
-        <v>794250</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>25416000</v>
+        <v>45000000</v>
       </c>
       <c r="AB21" t="n">
-        <v>1059000</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>26475000</v>
+        <v>45000000</v>
       </c>
       <c r="AD21" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-05 09:24:55</t>
+          <t>2026-10-06 11:22:10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2604,20 +2604,20 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>5816070</v>
+        <v>120000000</v>
       </c>
       <c r="H22" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2629,22 +2629,22 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>5234463</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>114000000</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2656,39 +2656,39 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>465285.6</v>
+        <v>6000000</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>5699748.6</v>
+        <v>120000000</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>5699748.6</v>
+        <v>120000000</v>
       </c>
       <c r="AB22" t="n">
-        <v>116321.4</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>5816070</v>
+        <v>120000000</v>
       </c>
       <c r="AD22" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-05 09:53:51</t>
+          <t>2026-10-06 11:43:08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>043/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2706,20 +2706,20 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>5816070</v>
+        <v>15000000</v>
       </c>
       <c r="H23" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>5234463</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>14250000</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -2758,39 +2758,39 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>465285.6</v>
+        <v>750000</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>5699748.6</v>
+        <v>15000000</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>5699748.6</v>
+        <v>15000000</v>
       </c>
       <c r="AB23" t="n">
-        <v>116321.4</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>5816070</v>
+        <v>15000000</v>
       </c>
       <c r="AD23" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-06 10:09:56</t>
+          <t>2026-10-06 12:31:17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>040/BSS-JOB/WS/IX/2026</t>
+          <t>044/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2808,11 +2808,11 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>22500000</v>
+        <v>12000000</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>21375000</v>
+        <v>11400000</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -2860,25 +2860,25 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1125000</v>
+        <v>600000</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>22500000</v>
+        <v>12000000</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>22500000</v>
+        <v>12000000</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>22500000</v>
+        <v>12000000</v>
       </c>
       <c r="AD24" t="n">
         <v>100</v>
@@ -2887,12 +2887,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-06 10:40:42</t>
+          <t>2026-10-06 13:00:47</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>041/BSS-JOB/WS/IX/2026</t>
+          <t>045/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2914,87 +2914,87 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>45000000</v>
+        <v>337500000</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>50625000</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>5062500</v>
       </c>
       <c r="S25" t="n">
-        <v>42750000</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>253125000</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>5062500</v>
       </c>
       <c r="W25" t="n">
-        <v>2250000</v>
+        <v>13500000</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>45000000</v>
+        <v>317250000</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>10125000</v>
       </c>
       <c r="AA25" t="n">
-        <v>45000000</v>
+        <v>327375000</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>10125000</v>
       </c>
       <c r="AC25" t="n">
-        <v>45000000</v>
+        <v>337500000</v>
       </c>
       <c r="AD25" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-06 11:22:10</t>
+          <t>2026-10-06 17:58:13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3016,7 +3016,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>120000000</v>
+        <v>11460000</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -3025,7 +3025,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -3037,13 +3037,13 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -3052,7 +3052,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>114000000</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -3064,39 +3064,39 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>6000000</v>
+        <v>11230800</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>120000000</v>
+        <v>11230800</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>120000000</v>
+        <v>11230800</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>229200</v>
       </c>
       <c r="AC26" t="n">
-        <v>120000000</v>
+        <v>11460000</v>
       </c>
       <c r="AD26" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-06 11:43:08</t>
+          <t>2026-10-06 18:53:41</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/WS/IX/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3114,20 +3114,20 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>15000000</v>
+        <v>15488550</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3139,22 +3139,22 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>13939695</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>14250000</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
@@ -3166,39 +3166,39 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>750000</v>
+        <v>1239084</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>15000000</v>
+        <v>15178779</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>15000000</v>
+        <v>15178779</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>309771</v>
       </c>
       <c r="AC27" t="n">
-        <v>15000000</v>
+        <v>15488550</v>
       </c>
       <c r="AD27" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-06 12:31:17</t>
+          <t>2026-10-06 19:07:28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>044/BSS-JOB/WS/IX/2026</t>
+          <t>050/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3216,11 +3216,11 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>12000000</v>
+        <v>69000000</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -3241,13 +3241,13 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -3256,7 +3256,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>11400000</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -3268,39 +3268,39 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>600000</v>
+        <v>67620000</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>12000000</v>
+        <v>67620000</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>12000000</v>
+        <v>67620000</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1380000</v>
       </c>
       <c r="AC28" t="n">
-        <v>12000000</v>
+        <v>69000000</v>
       </c>
       <c r="AD28" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-06 13:00:47</t>
+          <t>2026-10-07 06:17:59</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>045/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3322,13 +3322,13 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>337500000</v>
+        <v>192500000</v>
       </c>
       <c r="H29" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3337,25 +3337,25 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="M29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>50625000</v>
+        <v>9625000</v>
       </c>
       <c r="R29" t="n">
-        <v>5062500</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -3364,45 +3364,45 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>253125000</v>
+        <v>163625000</v>
       </c>
       <c r="V29" t="n">
-        <v>5062500</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>13500000</v>
+        <v>15400000</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>317250000</v>
+        <v>188650000</v>
       </c>
       <c r="Z29" t="n">
-        <v>10125000</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>327375000</v>
+        <v>188650000</v>
       </c>
       <c r="AB29" t="n">
-        <v>10125000</v>
+        <v>3850000</v>
       </c>
       <c r="AC29" t="n">
-        <v>337500000</v>
+        <v>192500000</v>
       </c>
       <c r="AD29" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-06 17:58:13</t>
+          <t>2026-10-07 09:02:12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3420,91 +3420,91 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>11460000</v>
+        <v>15200000</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N30" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2280000</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>228000</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>4256000</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>7296000</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>228000</v>
       </c>
       <c r="W30" t="n">
-        <v>11230800</v>
+        <v>304000</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>11230800</v>
+        <v>14136000</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>456000</v>
       </c>
       <c r="AA30" t="n">
-        <v>11230800</v>
+        <v>14592000</v>
       </c>
       <c r="AB30" t="n">
-        <v>229200</v>
+        <v>608000</v>
       </c>
       <c r="AC30" t="n">
-        <v>11460000</v>
+        <v>15200000</v>
       </c>
       <c r="AD30" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-06 18:53:41</t>
+          <t>2026-10-07 09:34:34</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -3522,91 +3522,91 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>15488550</v>
+        <v>30245000</v>
       </c>
       <c r="H31" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N31" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q31" t="n">
-        <v>13939695</v>
+        <v>4536750</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>453675</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>8468600</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>14517600</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>453675</v>
       </c>
       <c r="W31" t="n">
-        <v>1239084</v>
+        <v>604900</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>15178779</v>
+        <v>28127850</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>907350</v>
       </c>
       <c r="AA31" t="n">
-        <v>15178779</v>
+        <v>29035200</v>
       </c>
       <c r="AB31" t="n">
-        <v>309771</v>
+        <v>1209800</v>
       </c>
       <c r="AC31" t="n">
-        <v>15488550</v>
+        <v>30245000</v>
       </c>
       <c r="AD31" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-06 19:07:28</t>
+          <t>2026-10-07 10:43:34</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>050/BSS-JOB/WS/IX/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -3624,91 +3624,91 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>69000000</v>
+        <v>32335000</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N32" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4850250</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>485025</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>9053800</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>15520800</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>485025</v>
       </c>
       <c r="W32" t="n">
-        <v>67620000</v>
+        <v>646700</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>67620000</v>
+        <v>30071550</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>970050</v>
       </c>
       <c r="AA32" t="n">
-        <v>67620000</v>
+        <v>31041600</v>
       </c>
       <c r="AB32" t="n">
-        <v>1380000</v>
+        <v>1293400</v>
       </c>
       <c r="AC32" t="n">
-        <v>69000000</v>
+        <v>32335000</v>
       </c>
       <c r="AD32" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-07 06:17:59</t>
+          <t>2026-10-07 11:30:14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3726,91 +3726,91 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>192500000</v>
+        <v>20720000</v>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N33" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q33" t="n">
-        <v>9625000</v>
+        <v>3108000</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>310800</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>5801600.000000001</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>163625000</v>
+        <v>9945600</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>310800</v>
       </c>
       <c r="W33" t="n">
-        <v>15400000</v>
+        <v>414400</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>188650000</v>
+        <v>19269600</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>621600</v>
       </c>
       <c r="AA33" t="n">
-        <v>188650000</v>
+        <v>19891200</v>
       </c>
       <c r="AB33" t="n">
-        <v>3850000</v>
+        <v>828800</v>
       </c>
       <c r="AC33" t="n">
-        <v>192500000</v>
+        <v>20720000</v>
       </c>
       <c r="AD33" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-07 08:44:05</t>
+          <t>2026-10-10 08:59:37</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3828,11 +3828,11 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>15000000</v>
+        <v>198400000</v>
       </c>
       <c r="H34" t="n">
         <v>15</v>
@@ -3862,43 +3862,43 @@
         <v>4</v>
       </c>
       <c r="Q34" t="n">
-        <v>2250000</v>
+        <v>29760000</v>
       </c>
       <c r="R34" t="n">
-        <v>225000</v>
+        <v>2976000</v>
       </c>
       <c r="S34" t="n">
-        <v>4200000</v>
+        <v>55552000.00000001</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>7200000</v>
+        <v>95232000</v>
       </c>
       <c r="V34" t="n">
-        <v>225000</v>
+        <v>2976000</v>
       </c>
       <c r="W34" t="n">
-        <v>300000</v>
+        <v>3968000</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>13950000</v>
+        <v>184512000</v>
       </c>
       <c r="Z34" t="n">
-        <v>450000</v>
+        <v>5952000</v>
       </c>
       <c r="AA34" t="n">
-        <v>14400000</v>
+        <v>190464000</v>
       </c>
       <c r="AB34" t="n">
-        <v>600000</v>
+        <v>7936000</v>
       </c>
       <c r="AC34" t="n">
-        <v>15000000</v>
+        <v>198400000</v>
       </c>
       <c r="AD34" t="n">
         <v>93</v>
@@ -3907,12 +3907,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-07 09:02:12</t>
+          <t>2026-10-13 10:28:24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>051/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3930,91 +3930,91 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>15200000</v>
+        <v>1725000</v>
       </c>
       <c r="H35" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
+        <v>98</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
         <v>2</v>
       </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>4</v>
-      </c>
       <c r="Q35" t="n">
-        <v>2280000</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>228000</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>4256000</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>7296000</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>228000</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>304000</v>
+        <v>1690500</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>14136000</v>
+        <v>1690500</v>
       </c>
       <c r="Z35" t="n">
-        <v>456000</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>14592000</v>
+        <v>1690500</v>
       </c>
       <c r="AB35" t="n">
-        <v>608000</v>
+        <v>34500</v>
       </c>
       <c r="AC35" t="n">
-        <v>15200000</v>
+        <v>1725000</v>
       </c>
       <c r="AD35" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-07 09:34:34</t>
+          <t>2026-10-13 10:36:37</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>052/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4032,91 +4032,91 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>30245000</v>
+        <v>8625000</v>
       </c>
       <c r="H36" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
+        <v>98</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
         <v>2</v>
       </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>4</v>
-      </c>
       <c r="Q36" t="n">
-        <v>4536750</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>453675</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>8468600</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>14517600</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>453675</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>604900</v>
+        <v>8452500</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>28127850</v>
+        <v>8452500</v>
       </c>
       <c r="Z36" t="n">
-        <v>907350</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>29035200</v>
+        <v>8452500</v>
       </c>
       <c r="AB36" t="n">
-        <v>1209800</v>
+        <v>172500</v>
       </c>
       <c r="AC36" t="n">
-        <v>30245000</v>
+        <v>8625000</v>
       </c>
       <c r="AD36" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-07 10:43:34</t>
+          <t>2026-10-14 13:26:40</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>002/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011794</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4134,91 +4134,91 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>32335000</v>
+        <v>1437500</v>
       </c>
       <c r="H37" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
+        <v>8</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
         <v>2</v>
       </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>4</v>
-      </c>
       <c r="Q37" t="n">
-        <v>4850250</v>
+        <v>1293750</v>
       </c>
       <c r="R37" t="n">
-        <v>485025</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>9053800</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>15520800</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>485025</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>646700</v>
+        <v>115000</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>30071550</v>
+        <v>1408750</v>
       </c>
       <c r="Z37" t="n">
-        <v>970050</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>31041600</v>
+        <v>1408750</v>
       </c>
       <c r="AB37" t="n">
-        <v>1293400</v>
+        <v>28750</v>
       </c>
       <c r="AC37" t="n">
-        <v>32335000</v>
+        <v>1437500</v>
       </c>
       <c r="AD37" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-07 11:30:14</t>
+          <t>2026-10-14 13:54:24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>021/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011795</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4236,91 +4236,91 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>20720000</v>
+        <v>517499.9999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q38" t="n">
-        <v>3108000</v>
+        <v>439874.9999999999</v>
       </c>
       <c r="R38" t="n">
-        <v>310800</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>5801600.000000001</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>9945600</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>310800</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>414400</v>
+        <v>51749.99999999999</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>19269600</v>
+        <v>491624.9999999999</v>
       </c>
       <c r="Z38" t="n">
-        <v>621600</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>19891200</v>
+        <v>491624.9999999999</v>
       </c>
       <c r="AB38" t="n">
-        <v>828800</v>
+        <v>25875</v>
       </c>
       <c r="AC38" t="n">
-        <v>20720000</v>
+        <v>517499.9999999999</v>
       </c>
       <c r="AD38" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-10 08:59:37</t>
+          <t>2026-10-15 17:39:32</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -4333,96 +4333,96 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>198400000</v>
+        <v>205751000</v>
       </c>
       <c r="H39" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="M39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q39" t="n">
-        <v>29760000</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2976000</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>55552000.00000001</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>95232000</v>
+        <v>10287550</v>
       </c>
       <c r="V39" t="n">
-        <v>2976000</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>3968000</v>
+        <v>185175900</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>184512000</v>
+        <v>195463450</v>
       </c>
       <c r="Z39" t="n">
-        <v>5952000</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>190464000</v>
+        <v>195463450</v>
       </c>
       <c r="AB39" t="n">
-        <v>7936000</v>
+        <v>10287550</v>
       </c>
       <c r="AC39" t="n">
-        <v>198400000</v>
+        <v>205751000</v>
       </c>
       <c r="AD39" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-13 10:28:24</t>
+          <t>2026-10-15 17:45:36</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>051/BSS-JOB/WS/VIII/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -4430,21 +4430,21 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1725000</v>
+        <v>256779000</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -4465,13 +4465,13 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -4492,39 +4492,39 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1690500</v>
+        <v>243940050</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1690500</v>
+        <v>243940050</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1690500</v>
+        <v>243940050</v>
       </c>
       <c r="AB40" t="n">
-        <v>34500</v>
+        <v>12838950</v>
       </c>
       <c r="AC40" t="n">
-        <v>1725000</v>
+        <v>256779000</v>
       </c>
       <c r="AD40" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-13 10:36:37</t>
+          <t>2026-10-16 10:49:44</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>052/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4542,14 +4542,14 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>8625000</v>
+        <v>8803080</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -4567,16 +4567,16 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>7482618</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -4594,39 +4594,39 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>8452500</v>
+        <v>880308</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>8452500</v>
+        <v>8362926</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>8452500</v>
+        <v>8362926</v>
       </c>
       <c r="AB41" t="n">
-        <v>172500</v>
+        <v>440154</v>
       </c>
       <c r="AC41" t="n">
-        <v>8625000</v>
+        <v>8803080</v>
       </c>
       <c r="AD41" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-14 13:26:40</t>
+          <t>2026-10-16 10:59:17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/WS/I/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4500011794</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4644,14 +4644,14 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1437500</v>
+        <v>5816070</v>
       </c>
       <c r="H42" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -4669,16 +4669,16 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q42" t="n">
-        <v>1293750</v>
+        <v>4943659.5</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -4696,39 +4696,39 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>115000</v>
+        <v>581607</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1408750</v>
+        <v>5525266.5</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1408750</v>
+        <v>5525266.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>28750</v>
+        <v>290803.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>1437500</v>
+        <v>5816070</v>
       </c>
       <c r="AD42" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-14 13:54:24</t>
+          <t>2026-10-16 11:08:44</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>021/BSS-JOB/WS/IX/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4500011795</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4746,14 +4746,14 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>517499.9999999999</v>
+        <v>5816070</v>
       </c>
       <c r="H43" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -4771,16 +4771,16 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q43" t="n">
-        <v>439874.9999999999</v>
+        <v>5234463</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -4798,39 +4798,39 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>51749.99999999999</v>
+        <v>465285.6</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>491624.9999999999</v>
+        <v>5699748.6</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>491624.9999999999</v>
+        <v>5699748.6</v>
       </c>
       <c r="AB43" t="n">
-        <v>25875</v>
+        <v>116321.4</v>
       </c>
       <c r="AC43" t="n">
-        <v>517499.9999999999</v>
+        <v>5816070</v>
       </c>
       <c r="AD43" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-15 17:39:32</t>
+          <t>2026-10-16 11:30:53</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4848,14 +4848,14 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>205751000</v>
+        <v>5816070</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4867,22 +4867,22 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>5234463</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -4894,45 +4894,45 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>10287550</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>185175900</v>
+        <v>465285.6</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>195463450</v>
+        <v>5699748.6</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>195463450</v>
+        <v>5699748.6</v>
       </c>
       <c r="AB44" t="n">
-        <v>10287550</v>
+        <v>116321.4</v>
       </c>
       <c r="AC44" t="n">
-        <v>205751000</v>
+        <v>5816070</v>
       </c>
       <c r="AD44" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-15 17:45:36</t>
+          <t>2026-10-16 11:53:41</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4952,17 +4952,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>256779000</v>
+        <v>30000000</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4971,25 +4971,25 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N45" t="n">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4800000</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>450000</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -4998,34 +4998,34 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>22500000</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>450000</v>
       </c>
       <c r="W45" t="n">
-        <v>243940050</v>
+        <v>600000</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>243940050</v>
+        <v>27900000</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>900000</v>
       </c>
       <c r="AA45" t="n">
-        <v>243940050</v>
+        <v>28800000</v>
       </c>
       <c r="AB45" t="n">
-        <v>12838950</v>
+        <v>1200000</v>
       </c>
       <c r="AC45" t="n">
-        <v>256779000</v>
+        <v>30000000</v>
       </c>
       <c r="AD45" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
